--- a/backend/backend/data/IS_Questionnaires_revised_final version.xlsx
+++ b/backend/backend/data/IS_Questionnaires_revised_final version.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wjp713\Desktop\HAW\BIORADAR\Implementation Scorecard\T4.2 IS\Feedback\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ayushkhandelwal/Documents/Implementation-Scorecard/backend/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49292937-FA3E-4235-AE8D-D7B3E4304F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BFE882-56C3-834E-A6B3-C1A75BBFCBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{289CD14E-34B2-4390-AE6E-F3D0FBD6EA28}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="890">
   <si>
     <t>SDG</t>
   </si>
@@ -3233,7 +3233,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3432,48 +3432,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -3484,7 +3442,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3513,6 +3470,48 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3835,24 +3834,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF65FD75-B202-428F-9C36-7E65D5711C9E}">
   <dimension ref="B1:L103"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" style="52" customWidth="1"/>
+    <col min="1" max="1" width="14.5" style="52" customWidth="1"/>
     <col min="2" max="2" width="6" style="52" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.1796875" style="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.453125" style="52" customWidth="1"/>
-    <col min="5" max="5" width="25.453125" style="52" customWidth="1"/>
-    <col min="6" max="6" width="46.6328125" style="52" customWidth="1"/>
-    <col min="7" max="7" width="36.81640625" style="52" customWidth="1"/>
-    <col min="8" max="8" width="21.7265625" style="52" customWidth="1"/>
-    <col min="9" max="9" width="28.1796875" style="52" customWidth="1"/>
-    <col min="10" max="10" width="10.36328125" style="52" customWidth="1"/>
-    <col min="11" max="11" width="9.6328125" style="55" customWidth="1"/>
-    <col min="12" max="12" width="63.1796875" style="50" customWidth="1"/>
-    <col min="13" max="16384" width="8.81640625" style="52"/>
+    <col min="3" max="3" width="52.1640625" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="52" customWidth="1"/>
+    <col min="5" max="5" width="25.5" style="52" customWidth="1"/>
+    <col min="6" max="6" width="46.6640625" style="52" customWidth="1"/>
+    <col min="7" max="7" width="36.83203125" style="52" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" style="52" customWidth="1"/>
+    <col min="9" max="9" width="28.1640625" style="52" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="52" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" style="55" customWidth="1"/>
+    <col min="12" max="12" width="63.1640625" style="50" customWidth="1"/>
+    <col min="13" max="16384" width="8.83203125" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" s="26" customFormat="1" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" s="26" customFormat="1" ht="35.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="36" t="s">
         <v>0</v>
       </c>
@@ -3885,34 +3884,34 @@
       </c>
       <c r="L1" s="50"/>
     </row>
-    <row r="2" spans="2:12" s="26" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="86" t="s">
+    <row r="2" spans="2:12" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
       <c r="K2" s="54"/>
       <c r="L2" s="50"/>
     </row>
-    <row r="3" spans="2:12" s="26" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="83" t="s">
+    <row r="3" spans="2:12" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C3" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
       <c r="K3" s="54"/>
       <c r="L3" s="50"/>
     </row>
-    <row r="4" spans="2:12" s="26" customFormat="1" ht="93" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" s="26" customFormat="1" ht="102" x14ac:dyDescent="0.2">
       <c r="C4" s="14" t="s">
         <v>11</v>
       </c>
@@ -3936,7 +3935,7 @@
       <c r="K4" s="54"/>
       <c r="L4" s="50"/>
     </row>
-    <row r="5" spans="2:12" s="26" customFormat="1" ht="93" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" s="26" customFormat="1" ht="85" x14ac:dyDescent="0.2">
       <c r="C5" s="14" t="s">
         <v>16</v>
       </c>
@@ -3960,7 +3959,7 @@
       <c r="K5" s="54"/>
       <c r="L5" s="50"/>
     </row>
-    <row r="6" spans="2:12" s="26" customFormat="1" ht="86" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" s="26" customFormat="1" ht="86" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="14" t="s">
         <v>22</v>
       </c>
@@ -3986,7 +3985,7 @@
       </c>
       <c r="L6" s="50"/>
     </row>
-    <row r="7" spans="2:12" s="26" customFormat="1" ht="62" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" s="26" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="C7" s="14" t="s">
         <v>29</v>
       </c>
@@ -4010,30 +4009,30 @@
       <c r="K7" s="54"/>
       <c r="L7" s="50"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="84" t="s">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="84"/>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C9" s="83" t="s">
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C9" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-    </row>
-    <row r="10" spans="2:12" ht="80.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+    </row>
+    <row r="10" spans="2:12" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="32" t="s">
         <v>44</v>
       </c>
@@ -4055,7 +4054,7 @@
       </c>
       <c r="J10" s="68"/>
     </row>
-    <row r="11" spans="2:12" ht="93" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="85" x14ac:dyDescent="0.2">
       <c r="C11" s="65" t="s">
         <v>48</v>
       </c>
@@ -4077,7 +4076,7 @@
       </c>
       <c r="J11" s="67"/>
     </row>
-    <row r="12" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="85" x14ac:dyDescent="0.2">
       <c r="C12" s="14" t="s">
         <v>52</v>
       </c>
@@ -4099,7 +4098,7 @@
       </c>
       <c r="J12" s="67"/>
     </row>
-    <row r="13" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="68" x14ac:dyDescent="0.2">
       <c r="C13" s="14" t="s">
         <v>56</v>
       </c>
@@ -4121,30 +4120,30 @@
       </c>
       <c r="J13" s="68"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="84" t="s">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B14" s="93" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84"/>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="84"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="83" t="s">
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C15" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-    </row>
-    <row r="16" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D15" s="91"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+    </row>
+    <row r="16" spans="2:12" ht="85" x14ac:dyDescent="0.2">
       <c r="C16" s="14" t="s">
         <v>69</v>
       </c>
@@ -4164,7 +4163,7 @@
       <c r="I16" s="14"/>
       <c r="J16" s="68"/>
     </row>
-    <row r="17" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="C17" s="66" t="s">
         <v>72</v>
       </c>
@@ -4184,7 +4183,7 @@
       <c r="I17" s="14"/>
       <c r="J17" s="68"/>
     </row>
-    <row r="18" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="C18" s="66" t="s">
         <v>75</v>
       </c>
@@ -4205,7 +4204,7 @@
       <c r="J18" s="68"/>
       <c r="K18" s="54"/>
     </row>
-    <row r="19" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="C19" s="66" t="s">
         <v>78</v>
       </c>
@@ -4225,30 +4224,30 @@
       <c r="I19" s="14"/>
       <c r="J19" s="68"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B20" s="84" t="s">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B20" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="84"/>
-      <c r="G20" s="84"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="84"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C21" s="83" t="s">
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C21" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
-    </row>
-    <row r="22" spans="2:11" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="91"/>
+    </row>
+    <row r="22" spans="2:11" ht="85" x14ac:dyDescent="0.2">
       <c r="C22" s="66" t="s">
         <v>88</v>
       </c>
@@ -4268,7 +4267,7 @@
       <c r="I22" s="14"/>
       <c r="J22" s="68"/>
     </row>
-    <row r="23" spans="2:11" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" ht="51" x14ac:dyDescent="0.2">
       <c r="C23" s="66" t="s">
         <v>91</v>
       </c>
@@ -4288,7 +4287,7 @@
       <c r="I23" s="14"/>
       <c r="J23" s="68"/>
     </row>
-    <row r="24" spans="2:11" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" ht="85" x14ac:dyDescent="0.2">
       <c r="C24" s="66" t="s">
         <v>94</v>
       </c>
@@ -4309,7 +4308,7 @@
       <c r="J24" s="68"/>
       <c r="K24" s="54"/>
     </row>
-    <row r="25" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="C25" s="66" t="s">
         <v>97</v>
       </c>
@@ -4329,30 +4328,30 @@
       <c r="I25" s="14"/>
       <c r="J25" s="68"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B26" s="84" t="s">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B26" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="84"/>
-      <c r="G26" s="84"/>
-      <c r="H26" s="84"/>
-      <c r="I26" s="84"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C27" s="83" t="s">
+      <c r="C26" s="93"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C27" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-    </row>
-    <row r="28" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+      <c r="D27" s="91"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="91"/>
+      <c r="H27" s="91"/>
+      <c r="I27" s="91"/>
+    </row>
+    <row r="28" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="C28" s="14" t="s">
         <v>103</v>
       </c>
@@ -4372,7 +4371,7 @@
       <c r="I28" s="14"/>
       <c r="J28" s="68"/>
     </row>
-    <row r="29" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="C29" s="14" t="s">
         <v>106</v>
       </c>
@@ -4392,7 +4391,7 @@
       <c r="I29" s="14"/>
       <c r="J29" s="68"/>
     </row>
-    <row r="30" spans="2:11" ht="83" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:11" ht="83" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C30" s="14" t="s">
         <v>110</v>
       </c>
@@ -4415,7 +4414,7 @@
       <c r="J30" s="68"/>
       <c r="K30" s="54"/>
     </row>
-    <row r="31" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="C31" s="14" t="s">
         <v>113</v>
       </c>
@@ -4435,30 +4434,30 @@
       <c r="I31" s="14"/>
       <c r="J31" s="68"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B32" s="84" t="s">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B32" s="93" t="s">
         <v>118</v>
       </c>
-      <c r="C32" s="84"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="84"/>
-      <c r="G32" s="84"/>
-      <c r="H32" s="84"/>
-      <c r="I32" s="84"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="83" t="s">
+      <c r="C32" s="93"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C33" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-    </row>
-    <row r="34" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="D33" s="91"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+    </row>
+    <row r="34" spans="2:12" ht="68" x14ac:dyDescent="0.2">
       <c r="C34" s="14" t="s">
         <v>119</v>
       </c>
@@ -4480,7 +4479,7 @@
       </c>
       <c r="J34" s="68"/>
     </row>
-    <row r="35" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:12" ht="85" x14ac:dyDescent="0.2">
       <c r="C35" s="14" t="s">
         <v>123</v>
       </c>
@@ -4503,7 +4502,7 @@
       <c r="J35" s="68"/>
       <c r="K35" s="54"/>
     </row>
-    <row r="36" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:12" ht="68" x14ac:dyDescent="0.2">
       <c r="C36" s="14" t="s">
         <v>119</v>
       </c>
@@ -4523,7 +4522,7 @@
       <c r="I36" s="14"/>
       <c r="J36" s="68"/>
     </row>
-    <row r="37" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:12" ht="68" x14ac:dyDescent="0.2">
       <c r="C37" s="14" t="s">
         <v>130</v>
       </c>
@@ -4543,32 +4542,32 @@
       <c r="I37" s="14"/>
       <c r="J37" s="68"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B38" s="87" t="s">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B38" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="C38" s="87"/>
-      <c r="D38" s="87"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="87"/>
-      <c r="G38" s="87"/>
-      <c r="H38" s="87"/>
-      <c r="I38" s="87"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B39" s="88"/>
-      <c r="C39" s="83" t="s">
+      <c r="C38" s="95"/>
+      <c r="D38" s="95"/>
+      <c r="E38" s="95"/>
+      <c r="F38" s="95"/>
+      <c r="G38" s="95"/>
+      <c r="H38" s="95"/>
+      <c r="I38" s="95"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B39" s="96"/>
+      <c r="C39" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D39" s="83"/>
-      <c r="E39" s="83"/>
-      <c r="F39" s="83"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="83"/>
-    </row>
-    <row r="40" spans="2:12" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="88"/>
+      <c r="D39" s="91"/>
+      <c r="E39" s="91"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="91"/>
+      <c r="I39" s="91"/>
+    </row>
+    <row r="40" spans="2:12" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="96"/>
       <c r="C40" s="34" t="s">
         <v>145</v>
       </c>
@@ -4593,8 +4592,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="2:12" ht="62" x14ac:dyDescent="0.35">
-      <c r="B41" s="88"/>
+    <row r="41" spans="2:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="B41" s="96"/>
       <c r="C41" s="34" t="s">
         <v>151</v>
       </c>
@@ -4616,8 +4615,8 @@
       </c>
       <c r="J41" s="68"/>
     </row>
-    <row r="42" spans="2:12" ht="111.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="88"/>
+    <row r="42" spans="2:12" ht="111.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="96"/>
       <c r="C42" s="34" t="s">
         <v>145</v>
       </c>
@@ -4642,8 +4641,8 @@
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="B43" s="88"/>
+    <row r="43" spans="2:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="B43" s="96"/>
       <c r="C43" s="34" t="s">
         <v>145</v>
       </c>
@@ -4666,30 +4665,30 @@
       <c r="J43" s="68"/>
       <c r="K43" s="54"/>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B44" s="84" t="s">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B44" s="93" t="s">
         <v>178</v>
       </c>
-      <c r="C44" s="84"/>
-      <c r="D44" s="84"/>
-      <c r="E44" s="84"/>
-      <c r="F44" s="84"/>
-      <c r="G44" s="84"/>
-      <c r="H44" s="84"/>
-      <c r="I44" s="84"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C45" s="83" t="s">
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
+      <c r="F44" s="93"/>
+      <c r="G44" s="93"/>
+      <c r="H44" s="93"/>
+      <c r="I44" s="93"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C45" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D45" s="83"/>
-      <c r="E45" s="83"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="83"/>
-    </row>
-    <row r="46" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D45" s="91"/>
+      <c r="E45" s="91"/>
+      <c r="F45" s="91"/>
+      <c r="G45" s="91"/>
+      <c r="H45" s="91"/>
+      <c r="I45" s="91"/>
+    </row>
+    <row r="46" spans="2:12" ht="68" x14ac:dyDescent="0.2">
       <c r="C46" s="14" t="s">
         <v>180</v>
       </c>
@@ -4712,7 +4711,7 @@
       <c r="J46" s="68"/>
       <c r="L46" s="58"/>
     </row>
-    <row r="47" spans="2:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C47" s="14" t="s">
         <v>185</v>
       </c>
@@ -4735,7 +4734,7 @@
       <c r="J47" s="68"/>
       <c r="K47" s="54"/>
     </row>
-    <row r="48" spans="2:12" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:12" ht="51" x14ac:dyDescent="0.2">
       <c r="C48" s="14" t="s">
         <v>190</v>
       </c>
@@ -4757,7 +4756,7 @@
       </c>
       <c r="J48" s="68"/>
     </row>
-    <row r="49" spans="2:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C49" s="14" t="s">
         <v>195</v>
       </c>
@@ -4780,30 +4779,30 @@
       <c r="J49" s="68"/>
       <c r="K49" s="54"/>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B50" s="84" t="s">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B50" s="93" t="s">
         <v>210</v>
       </c>
-      <c r="C50" s="84"/>
-      <c r="D50" s="84"/>
-      <c r="E50" s="84"/>
-      <c r="F50" s="84"/>
-      <c r="G50" s="84"/>
-      <c r="H50" s="84"/>
-      <c r="I50" s="84"/>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C51" s="83" t="s">
+      <c r="C50" s="93"/>
+      <c r="D50" s="93"/>
+      <c r="E50" s="93"/>
+      <c r="F50" s="93"/>
+      <c r="G50" s="93"/>
+      <c r="H50" s="93"/>
+      <c r="I50" s="93"/>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C51" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="83"/>
-    </row>
-    <row r="52" spans="2:11" ht="88.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D51" s="91"/>
+      <c r="E51" s="91"/>
+      <c r="F51" s="91"/>
+      <c r="G51" s="91"/>
+      <c r="H51" s="91"/>
+      <c r="I51" s="91"/>
+    </row>
+    <row r="52" spans="2:11" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C52" s="70" t="s">
         <v>211</v>
       </c>
@@ -4825,7 +4824,7 @@
       </c>
       <c r="J52" s="68"/>
     </row>
-    <row r="53" spans="2:11" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:11" ht="51" x14ac:dyDescent="0.2">
       <c r="C53" s="70" t="s">
         <v>215</v>
       </c>
@@ -4845,7 +4844,7 @@
       <c r="I53" s="71"/>
       <c r="J53" s="68"/>
     </row>
-    <row r="54" spans="2:11" ht="71.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:11" ht="71.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C54" s="70" t="s">
         <v>218</v>
       </c>
@@ -4865,7 +4864,7 @@
       <c r="I54" s="72"/>
       <c r="J54" s="68"/>
     </row>
-    <row r="55" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="C55" s="70" t="s">
         <v>221</v>
       </c>
@@ -4885,30 +4884,30 @@
       <c r="I55" s="72"/>
       <c r="J55" s="68"/>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B56" s="84" t="s">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B56" s="93" t="s">
         <v>228</v>
       </c>
-      <c r="C56" s="84"/>
-      <c r="D56" s="84"/>
-      <c r="E56" s="84"/>
-      <c r="F56" s="84"/>
-      <c r="G56" s="84"/>
-      <c r="H56" s="84"/>
-      <c r="I56" s="84"/>
-    </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C57" s="83" t="s">
+      <c r="C56" s="93"/>
+      <c r="D56" s="93"/>
+      <c r="E56" s="93"/>
+      <c r="F56" s="93"/>
+      <c r="G56" s="93"/>
+      <c r="H56" s="93"/>
+      <c r="I56" s="93"/>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C57" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D57" s="83"/>
-      <c r="E57" s="83"/>
-      <c r="F57" s="83"/>
-      <c r="G57" s="83"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="83"/>
-    </row>
-    <row r="58" spans="2:11" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D57" s="91"/>
+      <c r="E57" s="91"/>
+      <c r="F57" s="91"/>
+      <c r="G57" s="91"/>
+      <c r="H57" s="91"/>
+      <c r="I57" s="91"/>
+    </row>
+    <row r="58" spans="2:11" ht="85" x14ac:dyDescent="0.2">
       <c r="C58" s="66" t="s">
         <v>229</v>
       </c>
@@ -4928,7 +4927,7 @@
       <c r="I58" s="69"/>
       <c r="J58" s="68"/>
     </row>
-    <row r="59" spans="2:11" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:11" ht="85" x14ac:dyDescent="0.2">
       <c r="C59" s="14" t="s">
         <v>232</v>
       </c>
@@ -4948,7 +4947,7 @@
       <c r="I59" s="69"/>
       <c r="J59" s="68"/>
     </row>
-    <row r="60" spans="2:11" ht="71.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:11" ht="71.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C60" s="66" t="s">
         <v>235</v>
       </c>
@@ -4965,10 +4964,10 @@
       <c r="H60" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="I60" s="89"/>
+      <c r="I60" s="92"/>
       <c r="J60" s="68"/>
     </row>
-    <row r="61" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="C61" s="66" t="s">
         <v>229</v>
       </c>
@@ -4985,33 +4984,33 @@
       <c r="H61" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="I61" s="89"/>
+      <c r="I61" s="92"/>
       <c r="J61" s="68"/>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B62" s="84" t="s">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B62" s="93" t="s">
         <v>242</v>
       </c>
-      <c r="C62" s="84"/>
-      <c r="D62" s="84"/>
-      <c r="E62" s="84"/>
-      <c r="F62" s="84"/>
-      <c r="G62" s="84"/>
-      <c r="H62" s="84"/>
-      <c r="I62" s="84"/>
-    </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C63" s="83" t="s">
+      <c r="C62" s="93"/>
+      <c r="D62" s="93"/>
+      <c r="E62" s="93"/>
+      <c r="F62" s="93"/>
+      <c r="G62" s="93"/>
+      <c r="H62" s="93"/>
+      <c r="I62" s="93"/>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C63" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D63" s="83"/>
-      <c r="E63" s="83"/>
-      <c r="F63" s="83"/>
-      <c r="G63" s="83"/>
-      <c r="H63" s="83"/>
-      <c r="I63" s="83"/>
-    </row>
-    <row r="64" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+      <c r="D63" s="91"/>
+      <c r="E63" s="91"/>
+      <c r="F63" s="91"/>
+      <c r="G63" s="91"/>
+      <c r="H63" s="91"/>
+      <c r="I63" s="91"/>
+    </row>
+    <row r="64" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="C64" s="34" t="s">
         <v>243</v>
       </c>
@@ -5033,7 +5032,7 @@
       </c>
       <c r="J64" s="68"/>
     </row>
-    <row r="65" spans="2:10" ht="62" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="C65" s="34" t="s">
         <v>247</v>
       </c>
@@ -5055,7 +5054,7 @@
       </c>
       <c r="J65" s="68"/>
     </row>
-    <row r="66" spans="2:10" ht="98.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" ht="98.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C66" s="34" t="s">
         <v>251</v>
       </c>
@@ -5077,7 +5076,7 @@
       </c>
       <c r="J66" s="68"/>
     </row>
-    <row r="67" spans="2:10" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" ht="85" x14ac:dyDescent="0.2">
       <c r="C67" s="34" t="s">
         <v>255</v>
       </c>
@@ -5099,30 +5098,30 @@
       </c>
       <c r="J67" s="68"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B68" s="84" t="s">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B68" s="93" t="s">
         <v>268</v>
       </c>
-      <c r="C68" s="84"/>
-      <c r="D68" s="84"/>
-      <c r="E68" s="84"/>
-      <c r="F68" s="84"/>
-      <c r="G68" s="84"/>
-      <c r="H68" s="84"/>
-      <c r="I68" s="84"/>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="C69" s="83" t="s">
+      <c r="C68" s="93"/>
+      <c r="D68" s="93"/>
+      <c r="E68" s="93"/>
+      <c r="F68" s="93"/>
+      <c r="G68" s="93"/>
+      <c r="H68" s="93"/>
+      <c r="I68" s="93"/>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C69" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D69" s="83"/>
-      <c r="E69" s="83"/>
-      <c r="F69" s="83"/>
-      <c r="G69" s="83"/>
-      <c r="H69" s="83"/>
-      <c r="I69" s="83"/>
-    </row>
-    <row r="70" spans="2:10" ht="88.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D69" s="91"/>
+      <c r="E69" s="91"/>
+      <c r="F69" s="91"/>
+      <c r="G69" s="91"/>
+      <c r="H69" s="91"/>
+      <c r="I69" s="91"/>
+    </row>
+    <row r="70" spans="2:10" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C70" s="34" t="s">
         <v>269</v>
       </c>
@@ -5144,7 +5143,7 @@
       </c>
       <c r="J70" s="68"/>
     </row>
-    <row r="71" spans="2:10" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="C71" s="34" t="s">
         <v>272</v>
       </c>
@@ -5166,7 +5165,7 @@
       </c>
       <c r="J71" s="68"/>
     </row>
-    <row r="72" spans="2:10" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="C72" s="34" t="s">
         <v>276</v>
       </c>
@@ -5183,12 +5182,12 @@
       <c r="H72" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="I72" s="85" t="s">
+      <c r="I72" s="97" t="s">
         <v>279</v>
       </c>
       <c r="J72" s="68"/>
     </row>
-    <row r="73" spans="2:10" ht="62" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="C73" s="34" t="s">
         <v>280</v>
       </c>
@@ -5205,33 +5204,33 @@
       <c r="H73" s="34" t="s">
         <v>282</v>
       </c>
-      <c r="I73" s="85"/>
+      <c r="I73" s="97"/>
       <c r="J73" s="68"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B74" s="84" t="s">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B74" s="93" t="s">
         <v>288</v>
       </c>
-      <c r="C74" s="84"/>
-      <c r="D74" s="84"/>
-      <c r="E74" s="84"/>
-      <c r="F74" s="84"/>
-      <c r="G74" s="84"/>
-      <c r="H74" s="84"/>
-      <c r="I74" s="84"/>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="C75" s="83" t="s">
+      <c r="C74" s="93"/>
+      <c r="D74" s="93"/>
+      <c r="E74" s="93"/>
+      <c r="F74" s="93"/>
+      <c r="G74" s="93"/>
+      <c r="H74" s="93"/>
+      <c r="I74" s="93"/>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C75" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D75" s="83"/>
-      <c r="E75" s="83"/>
-      <c r="F75" s="83"/>
-      <c r="G75" s="83"/>
-      <c r="H75" s="83"/>
-      <c r="I75" s="83"/>
-    </row>
-    <row r="76" spans="2:10" ht="92.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D75" s="91"/>
+      <c r="E75" s="91"/>
+      <c r="F75" s="91"/>
+      <c r="G75" s="91"/>
+      <c r="H75" s="91"/>
+      <c r="I75" s="91"/>
+    </row>
+    <row r="76" spans="2:10" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C76" s="32" t="s">
         <v>289</v>
       </c>
@@ -5253,7 +5252,7 @@
       </c>
       <c r="J76" s="68"/>
     </row>
-    <row r="77" spans="2:10" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:10" ht="51" x14ac:dyDescent="0.2">
       <c r="C77" s="32" t="s">
         <v>292</v>
       </c>
@@ -5273,7 +5272,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="68"/>
     </row>
-    <row r="78" spans="2:10" ht="62" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="C78" s="32" t="s">
         <v>289</v>
       </c>
@@ -5293,7 +5292,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="68"/>
     </row>
-    <row r="79" spans="2:10" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:10" ht="85" x14ac:dyDescent="0.2">
       <c r="C79" s="32" t="s">
         <v>297</v>
       </c>
@@ -5313,30 +5312,30 @@
       <c r="I79" s="75"/>
       <c r="J79" s="68"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B80" s="84" t="s">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B80" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="C80" s="84"/>
-      <c r="D80" s="84"/>
-      <c r="E80" s="84"/>
-      <c r="F80" s="84"/>
-      <c r="G80" s="84"/>
-      <c r="H80" s="84"/>
-      <c r="I80" s="84"/>
-    </row>
-    <row r="81" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C81" s="83" t="s">
+      <c r="C80" s="93"/>
+      <c r="D80" s="93"/>
+      <c r="E80" s="93"/>
+      <c r="F80" s="93"/>
+      <c r="G80" s="93"/>
+      <c r="H80" s="93"/>
+      <c r="I80" s="93"/>
+    </row>
+    <row r="81" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C81" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D81" s="83"/>
-      <c r="E81" s="83"/>
-      <c r="F81" s="83"/>
-      <c r="G81" s="83"/>
-      <c r="H81" s="83"/>
-      <c r="I81" s="83"/>
-    </row>
-    <row r="82" spans="2:10" ht="106" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D81" s="91"/>
+      <c r="E81" s="91"/>
+      <c r="F81" s="91"/>
+      <c r="G81" s="91"/>
+      <c r="H81" s="91"/>
+      <c r="I81" s="91"/>
+    </row>
+    <row r="82" spans="2:10" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C82" s="34" t="s">
         <v>303</v>
       </c>
@@ -5356,7 +5355,7 @@
       <c r="I82" s="57"/>
       <c r="J82" s="68"/>
     </row>
-    <row r="83" spans="2:10" ht="97.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C83" s="34" t="s">
         <v>306</v>
       </c>
@@ -5376,7 +5375,7 @@
       <c r="I83" s="56"/>
       <c r="J83" s="68"/>
     </row>
-    <row r="84" spans="2:10" ht="62" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="C84" s="34" t="s">
         <v>306</v>
       </c>
@@ -5396,7 +5395,7 @@
       <c r="I84" s="56"/>
       <c r="J84" s="68"/>
     </row>
-    <row r="85" spans="2:10" ht="62" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="C85" s="34" t="s">
         <v>533</v>
       </c>
@@ -5416,30 +5415,30 @@
       <c r="I85" s="56"/>
       <c r="J85" s="68"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B86" s="84" t="s">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B86" s="93" t="s">
         <v>319</v>
       </c>
-      <c r="C86" s="84"/>
-      <c r="D86" s="84"/>
-      <c r="E86" s="84"/>
-      <c r="F86" s="84"/>
-      <c r="G86" s="84"/>
-      <c r="H86" s="84"/>
-      <c r="I86" s="84"/>
-    </row>
-    <row r="87" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C87" s="83" t="s">
+      <c r="C86" s="93"/>
+      <c r="D86" s="93"/>
+      <c r="E86" s="93"/>
+      <c r="F86" s="93"/>
+      <c r="G86" s="93"/>
+      <c r="H86" s="93"/>
+      <c r="I86" s="93"/>
+    </row>
+    <row r="87" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C87" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D87" s="83"/>
-      <c r="E87" s="83"/>
-      <c r="F87" s="83"/>
-      <c r="G87" s="83"/>
-      <c r="H87" s="83"/>
-      <c r="I87" s="83"/>
-    </row>
-    <row r="88" spans="2:10" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D87" s="91"/>
+      <c r="E87" s="91"/>
+      <c r="F87" s="91"/>
+      <c r="G87" s="91"/>
+      <c r="H87" s="91"/>
+      <c r="I87" s="91"/>
+    </row>
+    <row r="88" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="C88" s="32" t="s">
         <v>320</v>
       </c>
@@ -5459,7 +5458,7 @@
       <c r="I88" s="74"/>
       <c r="J88" s="68"/>
     </row>
-    <row r="89" spans="2:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C89" s="32" t="s">
         <v>323</v>
       </c>
@@ -5479,7 +5478,7 @@
       <c r="I89" s="73"/>
       <c r="J89" s="68"/>
     </row>
-    <row r="90" spans="2:10" ht="62" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="C90" s="32" t="s">
         <v>326</v>
       </c>
@@ -5499,7 +5498,7 @@
       <c r="I90" s="73"/>
       <c r="J90" s="68"/>
     </row>
-    <row r="91" spans="2:10" ht="77.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:10" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C91" s="32" t="s">
         <v>323</v>
       </c>
@@ -5519,30 +5518,30 @@
       <c r="I91" s="73"/>
       <c r="J91" s="68"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B92" s="84" t="s">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B92" s="93" t="s">
         <v>338</v>
       </c>
-      <c r="C92" s="84"/>
-      <c r="D92" s="84"/>
-      <c r="E92" s="84"/>
-      <c r="F92" s="84"/>
-      <c r="G92" s="84"/>
-      <c r="H92" s="84"/>
-      <c r="I92" s="84"/>
-    </row>
-    <row r="93" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C93" s="83" t="s">
+      <c r="C92" s="93"/>
+      <c r="D92" s="93"/>
+      <c r="E92" s="93"/>
+      <c r="F92" s="93"/>
+      <c r="G92" s="93"/>
+      <c r="H92" s="93"/>
+      <c r="I92" s="93"/>
+    </row>
+    <row r="93" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C93" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D93" s="83"/>
-      <c r="E93" s="83"/>
-      <c r="F93" s="83"/>
-      <c r="G93" s="83"/>
-      <c r="H93" s="83"/>
-      <c r="I93" s="83"/>
-    </row>
-    <row r="94" spans="2:10" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="D93" s="91"/>
+      <c r="E93" s="91"/>
+      <c r="F93" s="91"/>
+      <c r="G93" s="91"/>
+      <c r="H93" s="91"/>
+      <c r="I93" s="91"/>
+    </row>
+    <row r="94" spans="2:10" ht="51" x14ac:dyDescent="0.2">
       <c r="C94" s="32" t="s">
         <v>339</v>
       </c>
@@ -5562,7 +5561,7 @@
       <c r="I94" s="57"/>
       <c r="J94" s="68"/>
     </row>
-    <row r="95" spans="2:10" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:10" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C95" s="32" t="s">
         <v>342</v>
       </c>
@@ -5582,7 +5581,7 @@
       <c r="I95" s="56"/>
       <c r="J95" s="68"/>
     </row>
-    <row r="96" spans="2:10" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:10" ht="51" x14ac:dyDescent="0.2">
       <c r="C96" s="32" t="s">
         <v>339</v>
       </c>
@@ -5602,7 +5601,7 @@
       <c r="I96" s="56"/>
       <c r="J96" s="68"/>
     </row>
-    <row r="97" spans="2:10" ht="80.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:10" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C97" s="32" t="s">
         <v>347</v>
       </c>
@@ -5622,30 +5621,30 @@
       <c r="I97" s="56"/>
       <c r="J97" s="68"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B98" s="84" t="s">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B98" s="93" t="s">
         <v>357</v>
       </c>
-      <c r="C98" s="84"/>
-      <c r="D98" s="84"/>
-      <c r="E98" s="84"/>
-      <c r="F98" s="84"/>
-      <c r="G98" s="84"/>
-      <c r="H98" s="84"/>
-      <c r="I98" s="84"/>
-    </row>
-    <row r="99" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="83" t="s">
+      <c r="C98" s="93"/>
+      <c r="D98" s="93"/>
+      <c r="E98" s="93"/>
+      <c r="F98" s="93"/>
+      <c r="G98" s="93"/>
+      <c r="H98" s="93"/>
+      <c r="I98" s="93"/>
+    </row>
+    <row r="99" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C99" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="D99" s="83"/>
-      <c r="E99" s="83"/>
-      <c r="F99" s="83"/>
-      <c r="G99" s="83"/>
-      <c r="H99" s="83"/>
-      <c r="I99" s="83"/>
-    </row>
-    <row r="100" spans="2:10" ht="93" x14ac:dyDescent="0.35">
+      <c r="D99" s="91"/>
+      <c r="E99" s="91"/>
+      <c r="F99" s="91"/>
+      <c r="G99" s="91"/>
+      <c r="H99" s="91"/>
+      <c r="I99" s="91"/>
+    </row>
+    <row r="100" spans="2:10" ht="85" x14ac:dyDescent="0.2">
       <c r="C100" s="34" t="s">
         <v>358</v>
       </c>
@@ -5665,7 +5664,7 @@
       <c r="I100" s="57"/>
       <c r="J100" s="68"/>
     </row>
-    <row r="101" spans="2:10" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:10" ht="85" x14ac:dyDescent="0.2">
       <c r="C101" s="34" t="s">
         <v>360</v>
       </c>
@@ -5685,7 +5684,7 @@
       <c r="I101" s="56"/>
       <c r="J101" s="68"/>
     </row>
-    <row r="102" spans="2:10" ht="118.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:10" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C102" s="34" t="s">
         <v>363</v>
       </c>
@@ -5705,7 +5704,7 @@
       <c r="I102" s="56"/>
       <c r="J102" s="68"/>
     </row>
-    <row r="103" spans="2:10" ht="93" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:10" ht="85" x14ac:dyDescent="0.2">
       <c r="C103" s="34" t="s">
         <v>550</v>
       </c>
@@ -5727,13 +5726,20 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="C57:I57"/>
-    <mergeCell ref="I60:I61"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="C51:I51"/>
-    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="C99:I99"/>
+    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="C87:I87"/>
+    <mergeCell ref="B92:I92"/>
+    <mergeCell ref="C93:I93"/>
+    <mergeCell ref="B98:I98"/>
+    <mergeCell ref="C63:I63"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="C75:I75"/>
+    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="C69:I69"/>
+    <mergeCell ref="I72:I73"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="B26:I26"/>
@@ -5750,20 +5756,13 @@
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="B39:B43"/>
     <mergeCell ref="C39:I39"/>
-    <mergeCell ref="C63:I63"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="C75:I75"/>
-    <mergeCell ref="B80:I80"/>
-    <mergeCell ref="C81:I81"/>
-    <mergeCell ref="B68:I68"/>
-    <mergeCell ref="C69:I69"/>
-    <mergeCell ref="I72:I73"/>
-    <mergeCell ref="C99:I99"/>
-    <mergeCell ref="B86:I86"/>
-    <mergeCell ref="C87:I87"/>
-    <mergeCell ref="B92:I92"/>
-    <mergeCell ref="C93:I93"/>
-    <mergeCell ref="B98:I98"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="C51:I51"/>
+    <mergeCell ref="B56:I56"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I70" r:id="rId1" display="https://www.europarl.europa.eu/topics/en/article/20201208STO93327/the-impact-of-textile-production-and-waste-on-the-environment-infographics" xr:uid="{58127E62-C780-41CE-A73E-544FB54369FD}"/>
@@ -5789,24 +5788,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EF2432C-E0D3-460A-9D2E-88007CDED581}">
   <dimension ref="B1:T103"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="8.7265625" style="39"/>
-    <col min="3" max="3" width="48.1796875" style="39" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="48.1796875" style="13" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="13" customWidth="1"/>
-    <col min="6" max="6" width="25.453125" style="13" customWidth="1"/>
-    <col min="7" max="7" width="46.6328125" style="13" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" style="39"/>
+    <col min="3" max="3" width="48.1640625" style="39" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="48.1640625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" style="13" customWidth="1"/>
+    <col min="6" max="6" width="25.5" style="13" customWidth="1"/>
+    <col min="7" max="7" width="46.6640625" style="13" customWidth="1"/>
     <col min="8" max="8" width="44" style="13" customWidth="1"/>
-    <col min="9" max="9" width="29.7265625" style="13" customWidth="1"/>
-    <col min="10" max="10" width="28.90625" style="13" customWidth="1"/>
-    <col min="11" max="11" width="8.7265625" style="39"/>
+    <col min="9" max="9" width="29.6640625" style="13" customWidth="1"/>
+    <col min="10" max="10" width="28.83203125" style="13" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" style="39"/>
     <col min="12" max="12" width="30" style="39" customWidth="1"/>
-    <col min="13" max="13" width="9.1796875" style="39" customWidth="1"/>
-    <col min="14" max="16384" width="8.7265625" style="39"/>
+    <col min="13" max="13" width="9.1640625" style="39" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="31" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="34" x14ac:dyDescent="0.2">
       <c r="B1" s="36" t="s">
         <v>0</v>
       </c>
@@ -5841,32 +5840,32 @@
         <v>386</v>
       </c>
     </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B2" s="79" t="s">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B2" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="C3" s="81" t="s">
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="C3" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-    </row>
-    <row r="4" spans="2:17" ht="62" x14ac:dyDescent="0.35">
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+    </row>
+    <row r="4" spans="2:17" ht="68" x14ac:dyDescent="0.2">
       <c r="D4" s="20" t="s">
         <v>388</v>
       </c>
@@ -5888,7 +5887,7 @@
       </c>
       <c r="K4" s="59"/>
     </row>
-    <row r="5" spans="2:17" ht="93" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:17" ht="85" x14ac:dyDescent="0.2">
       <c r="D5" s="20" t="s">
         <v>388</v>
       </c>
@@ -5909,13 +5908,13 @@
         <v>20</v>
       </c>
       <c r="K5" s="59"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-    </row>
-    <row r="6" spans="2:17" ht="62" x14ac:dyDescent="0.35">
+      <c r="M5" s="100"/>
+      <c r="N5" s="100"/>
+      <c r="O5" s="100"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+    </row>
+    <row r="6" spans="2:17" ht="51" x14ac:dyDescent="0.2">
       <c r="D6" s="20" t="s">
         <v>390</v>
       </c>
@@ -5937,7 +5936,7 @@
       </c>
       <c r="K6" s="59"/>
     </row>
-    <row r="7" spans="2:17" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:17" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="20" t="s">
         <v>28</v>
       </c>
@@ -5963,32 +5962,32 @@
       <c r="K7" s="59"/>
       <c r="L7" s="13"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B8" s="79" t="s">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B8" s="99" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="79"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="C9" s="81" t="s">
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="C9" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="81"/>
-    </row>
-    <row r="10" spans="2:17" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="98"/>
+    </row>
+    <row r="10" spans="2:17" ht="51" x14ac:dyDescent="0.2">
       <c r="D10" s="20" t="s">
         <v>395</v>
       </c>
@@ -6010,7 +6009,7 @@
       </c>
       <c r="K10" s="59"/>
     </row>
-    <row r="11" spans="2:17" ht="62" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:17" ht="68" x14ac:dyDescent="0.2">
       <c r="D11" s="32" t="s">
         <v>396</v>
       </c>
@@ -6032,7 +6031,7 @@
       </c>
       <c r="K11" s="59"/>
     </row>
-    <row r="12" spans="2:17" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:17" ht="85" x14ac:dyDescent="0.2">
       <c r="D12" s="20" t="s">
         <v>52</v>
       </c>
@@ -6052,7 +6051,7 @@
       <c r="J12" s="20"/>
       <c r="K12" s="59"/>
     </row>
-    <row r="13" spans="2:17" ht="62" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:17" ht="68" x14ac:dyDescent="0.2">
       <c r="D13" s="20" t="s">
         <v>394</v>
       </c>
@@ -6074,32 +6073,32 @@
       </c>
       <c r="K13" s="59"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B14" s="79" t="s">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B14" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="C15" s="81" t="s">
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="99"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="C15" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-    </row>
-    <row r="16" spans="2:17" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="98"/>
+      <c r="I15" s="98"/>
+      <c r="J15" s="98"/>
+    </row>
+    <row r="16" spans="2:17" ht="68" x14ac:dyDescent="0.2">
       <c r="D16" s="60" t="s">
         <v>81</v>
       </c>
@@ -6119,7 +6118,7 @@
       <c r="J16" s="20"/>
       <c r="K16" s="59"/>
     </row>
-    <row r="17" spans="2:20" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:20" ht="77.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D17" s="60" t="s">
         <v>84</v>
       </c>
@@ -6139,7 +6138,7 @@
       <c r="J17" s="20"/>
       <c r="K17" s="59"/>
     </row>
-    <row r="18" spans="2:20" ht="93" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:20" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D18" s="60" t="s">
         <v>402</v>
       </c>
@@ -6160,7 +6159,7 @@
       <c r="K18" s="59"/>
       <c r="L18" s="46"/>
     </row>
-    <row r="19" spans="2:20" ht="62" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:20" ht="51" x14ac:dyDescent="0.2">
       <c r="D19" s="60" t="s">
         <v>78</v>
       </c>
@@ -6181,32 +6180,32 @@
       <c r="K19" s="59"/>
       <c r="L19" s="47"/>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B20" s="79" t="s">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B20" s="99" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C21" s="81" t="s">
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="99"/>
+      <c r="H20" s="99"/>
+      <c r="I20" s="99"/>
+      <c r="J20" s="99"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C21" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-    </row>
-    <row r="22" spans="2:20" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="98"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="98"/>
+    </row>
+    <row r="22" spans="2:20" ht="51" x14ac:dyDescent="0.2">
       <c r="D22" s="20" t="s">
         <v>409</v>
       </c>
@@ -6226,7 +6225,7 @@
       <c r="J22" s="20"/>
       <c r="K22" s="59"/>
     </row>
-    <row r="23" spans="2:20" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:20" ht="77.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D23" s="20" t="s">
         <v>410</v>
       </c>
@@ -6247,7 +6246,7 @@
       <c r="K23" s="59"/>
       <c r="L23" s="47"/>
     </row>
-    <row r="24" spans="2:20" ht="93" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:20" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="60" t="s">
         <v>94</v>
       </c>
@@ -6268,7 +6267,7 @@
       <c r="K24" s="59"/>
       <c r="L24" s="46"/>
     </row>
-    <row r="25" spans="2:20" ht="62" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:20" ht="68" x14ac:dyDescent="0.2">
       <c r="D25" s="20" t="s">
         <v>408</v>
       </c>
@@ -6289,32 +6288,32 @@
       <c r="K25" s="59"/>
       <c r="L25" s="47"/>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B26" s="79" t="s">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B26" s="99" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="79"/>
-      <c r="H26" s="79"/>
-      <c r="I26" s="79"/>
-      <c r="J26" s="79"/>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C27" s="81" t="s">
+      <c r="C26" s="99"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="99"/>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C27" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="81"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="81"/>
-    </row>
-    <row r="28" spans="2:20" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="98"/>
+      <c r="I27" s="98"/>
+      <c r="J27" s="98"/>
+    </row>
+    <row r="28" spans="2:20" ht="68" x14ac:dyDescent="0.2">
       <c r="D28" s="20" t="s">
         <v>116</v>
       </c>
@@ -6333,16 +6332,16 @@
       </c>
       <c r="J28" s="20"/>
       <c r="K28" s="59"/>
-      <c r="M28" s="78"/>
-      <c r="N28" s="78"/>
-      <c r="O28" s="78"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
-      <c r="R28" s="78"/>
-      <c r="S28" s="78"/>
-      <c r="T28" s="78"/>
-    </row>
-    <row r="29" spans="2:20" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M28" s="100"/>
+      <c r="N28" s="100"/>
+      <c r="O28" s="100"/>
+      <c r="P28" s="100"/>
+      <c r="Q28" s="100"/>
+      <c r="R28" s="100"/>
+      <c r="S28" s="100"/>
+      <c r="T28" s="100"/>
+    </row>
+    <row r="29" spans="2:20" ht="77.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D29" s="20" t="s">
         <v>106</v>
       </c>
@@ -6362,7 +6361,7 @@
       <c r="J29" s="20"/>
       <c r="K29" s="59"/>
     </row>
-    <row r="30" spans="2:20" ht="93" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:20" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D30" s="20" t="s">
         <v>110</v>
       </c>
@@ -6381,9 +6380,9 @@
       </c>
       <c r="J30" s="20"/>
       <c r="K30" s="59"/>
-      <c r="L30" s="80"/>
-    </row>
-    <row r="31" spans="2:20" ht="62.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L30" s="101"/>
+    </row>
+    <row r="31" spans="2:20" ht="62.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D31" s="20" t="s">
         <v>113</v>
       </c>
@@ -6402,34 +6401,34 @@
       </c>
       <c r="J31" s="20"/>
       <c r="K31" s="59"/>
-      <c r="L31" s="80"/>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B32" s="79" t="s">
+      <c r="L31" s="101"/>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B32" s="99" t="s">
         <v>118</v>
       </c>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="79"/>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C33" s="81" t="s">
+      <c r="C32" s="99"/>
+      <c r="D32" s="99"/>
+      <c r="E32" s="99"/>
+      <c r="F32" s="99"/>
+      <c r="G32" s="99"/>
+      <c r="H32" s="99"/>
+      <c r="I32" s="99"/>
+      <c r="J32" s="99"/>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C33" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="81"/>
-    </row>
-    <row r="34" spans="2:20" ht="93" x14ac:dyDescent="0.35">
+      <c r="D33" s="98"/>
+      <c r="E33" s="98"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="98"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="98"/>
+      <c r="J33" s="98"/>
+    </row>
+    <row r="34" spans="2:20" ht="68" x14ac:dyDescent="0.2">
       <c r="D34" s="20" t="s">
         <v>129</v>
       </c>
@@ -6449,7 +6448,7 @@
       <c r="J34" s="20"/>
       <c r="K34" s="59"/>
     </row>
-    <row r="35" spans="2:20" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:20" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D35" s="20" t="s">
         <v>123</v>
       </c>
@@ -6471,7 +6470,7 @@
       </c>
       <c r="K35" s="59"/>
     </row>
-    <row r="36" spans="2:20" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:20" ht="51" x14ac:dyDescent="0.2">
       <c r="D36" s="20" t="s">
         <v>129</v>
       </c>
@@ -6492,7 +6491,7 @@
       <c r="K36" s="59"/>
       <c r="L36" s="47"/>
     </row>
-    <row r="37" spans="2:20" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:20" ht="68" x14ac:dyDescent="0.2">
       <c r="D37" s="20" t="s">
         <v>422</v>
       </c>
@@ -6513,40 +6512,40 @@
         <v>424</v>
       </c>
       <c r="K37" s="59"/>
-      <c r="M37" s="78"/>
-      <c r="N37" s="78"/>
-      <c r="P37" s="78"/>
-      <c r="Q37" s="78"/>
-      <c r="R37" s="78"/>
-      <c r="S37" s="78"/>
-      <c r="T37" s="78"/>
-    </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B38" s="79" t="s">
+      <c r="M37" s="100"/>
+      <c r="N37" s="100"/>
+      <c r="P37" s="100"/>
+      <c r="Q37" s="100"/>
+      <c r="R37" s="100"/>
+      <c r="S37" s="100"/>
+      <c r="T37" s="100"/>
+    </row>
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B38" s="99" t="s">
         <v>143</v>
       </c>
-      <c r="C38" s="79"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="79"/>
-      <c r="J38" s="79"/>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C39" s="81" t="s">
+      <c r="C38" s="99"/>
+      <c r="D38" s="99"/>
+      <c r="E38" s="99"/>
+      <c r="F38" s="99"/>
+      <c r="G38" s="99"/>
+      <c r="H38" s="99"/>
+      <c r="I38" s="99"/>
+      <c r="J38" s="99"/>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C39" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D39" s="81"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="81"/>
-      <c r="I39" s="81"/>
-      <c r="J39" s="81"/>
-    </row>
-    <row r="40" spans="2:20" ht="62" x14ac:dyDescent="0.35">
+      <c r="D39" s="98"/>
+      <c r="E39" s="98"/>
+      <c r="F39" s="98"/>
+      <c r="G39" s="98"/>
+      <c r="H39" s="98"/>
+      <c r="I39" s="98"/>
+      <c r="J39" s="98"/>
+    </row>
+    <row r="40" spans="2:20" ht="68" x14ac:dyDescent="0.2">
       <c r="B40" s="43"/>
       <c r="C40" s="24" t="s">
         <v>144</v>
@@ -6573,12 +6572,12 @@
       <c r="K40" s="59"/>
       <c r="L40" s="48"/>
       <c r="M40" s="20"/>
-      <c r="N40" s="78"/>
-      <c r="O40" s="78"/>
-      <c r="P40" s="78"/>
-      <c r="Q40" s="78"/>
-    </row>
-    <row r="41" spans="2:20" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="N40" s="100"/>
+      <c r="O40" s="100"/>
+      <c r="P40" s="100"/>
+      <c r="Q40" s="100"/>
+    </row>
+    <row r="41" spans="2:20" ht="51" x14ac:dyDescent="0.2">
       <c r="B41" s="43"/>
       <c r="C41" s="24" t="s">
         <v>150</v>
@@ -6605,12 +6604,12 @@
       <c r="K41" s="59"/>
       <c r="L41" s="13"/>
       <c r="M41" s="20"/>
-      <c r="N41" s="78"/>
-      <c r="O41" s="78"/>
-      <c r="P41" s="78"/>
-      <c r="Q41" s="78"/>
-    </row>
-    <row r="42" spans="2:20" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="N41" s="100"/>
+      <c r="O41" s="100"/>
+      <c r="P41" s="100"/>
+      <c r="Q41" s="100"/>
+    </row>
+    <row r="42" spans="2:20" ht="102" x14ac:dyDescent="0.2">
       <c r="B42" s="43"/>
       <c r="C42" s="20" t="s">
         <v>155</v>
@@ -6638,7 +6637,7 @@
       <c r="L42" s="48"/>
       <c r="M42" s="20"/>
     </row>
-    <row r="43" spans="2:20" ht="126.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:20" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="43"/>
       <c r="C43" s="20" t="s">
         <v>163</v>
@@ -6666,32 +6665,32 @@
       <c r="L43" s="48"/>
       <c r="M43" s="20"/>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B44" s="79" t="s">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B44" s="99" t="s">
         <v>178</v>
       </c>
-      <c r="C44" s="79"/>
-      <c r="D44" s="79"/>
-      <c r="E44" s="79"/>
-      <c r="F44" s="79"/>
-      <c r="G44" s="79"/>
-      <c r="H44" s="79"/>
-      <c r="I44" s="79"/>
-      <c r="J44" s="79"/>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C45" s="81" t="s">
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="99"/>
+      <c r="H44" s="99"/>
+      <c r="I44" s="99"/>
+      <c r="J44" s="99"/>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C45" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="81"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81"/>
-      <c r="H45" s="81"/>
-      <c r="I45" s="81"/>
-      <c r="J45" s="81"/>
-    </row>
-    <row r="46" spans="2:20" ht="78" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D45" s="98"/>
+      <c r="E45" s="98"/>
+      <c r="F45" s="98"/>
+      <c r="G45" s="98"/>
+      <c r="H45" s="98"/>
+      <c r="I45" s="98"/>
+      <c r="J45" s="98"/>
+    </row>
+    <row r="46" spans="2:20" ht="78" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C46" s="13" t="s">
         <v>179</v>
       </c>
@@ -6716,7 +6715,7 @@
       </c>
       <c r="K46" s="59"/>
     </row>
-    <row r="47" spans="2:20" ht="97.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:20" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C47" s="13" t="s">
         <v>184</v>
       </c>
@@ -6740,12 +6739,12 @@
         <v>205</v>
       </c>
       <c r="K47" s="59"/>
-      <c r="N47" s="78"/>
-      <c r="O47" s="78"/>
-      <c r="P47" s="78"/>
-      <c r="Q47" s="78"/>
-    </row>
-    <row r="48" spans="2:20" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="N47" s="100"/>
+      <c r="O47" s="100"/>
+      <c r="P47" s="100"/>
+      <c r="Q47" s="100"/>
+    </row>
+    <row r="48" spans="2:20" ht="85" x14ac:dyDescent="0.2">
       <c r="C48" s="13" t="s">
         <v>189</v>
       </c>
@@ -6771,7 +6770,7 @@
       <c r="K48" s="59"/>
       <c r="L48" s="46"/>
     </row>
-    <row r="49" spans="2:19" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:19" ht="68" x14ac:dyDescent="0.2">
       <c r="C49" s="13" t="s">
         <v>194</v>
       </c>
@@ -6794,39 +6793,39 @@
       <c r="J49" s="20"/>
       <c r="K49" s="59"/>
       <c r="L49" s="47"/>
-      <c r="N49" s="78"/>
-      <c r="O49" s="78"/>
-      <c r="P49" s="78"/>
-      <c r="Q49" s="78"/>
-      <c r="R49" s="78"/>
-      <c r="S49" s="78"/>
-    </row>
-    <row r="50" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B50" s="79" t="s">
+      <c r="N49" s="100"/>
+      <c r="O49" s="100"/>
+      <c r="P49" s="100"/>
+      <c r="Q49" s="100"/>
+      <c r="R49" s="100"/>
+      <c r="S49" s="100"/>
+    </row>
+    <row r="50" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B50" s="99" t="s">
         <v>210</v>
       </c>
-      <c r="C50" s="79"/>
-      <c r="D50" s="79"/>
-      <c r="E50" s="79"/>
-      <c r="F50" s="79"/>
-      <c r="G50" s="79"/>
-      <c r="H50" s="79"/>
-      <c r="I50" s="79"/>
-      <c r="J50" s="79"/>
-    </row>
-    <row r="51" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C51" s="81" t="s">
+      <c r="C50" s="99"/>
+      <c r="D50" s="99"/>
+      <c r="E50" s="99"/>
+      <c r="F50" s="99"/>
+      <c r="G50" s="99"/>
+      <c r="H50" s="99"/>
+      <c r="I50" s="99"/>
+      <c r="J50" s="99"/>
+    </row>
+    <row r="51" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="C51" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D51" s="81"/>
-      <c r="E51" s="81"/>
-      <c r="F51" s="81"/>
-      <c r="G51" s="81"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="81"/>
-      <c r="J51" s="81"/>
-    </row>
-    <row r="52" spans="2:19" ht="62" x14ac:dyDescent="0.35">
+      <c r="D51" s="98"/>
+      <c r="E51" s="98"/>
+      <c r="F51" s="98"/>
+      <c r="G51" s="98"/>
+      <c r="H51" s="98"/>
+      <c r="I51" s="98"/>
+      <c r="J51" s="98"/>
+    </row>
+    <row r="52" spans="2:19" ht="68" x14ac:dyDescent="0.2">
       <c r="D52" s="60" t="s">
         <v>211</v>
       </c>
@@ -6846,7 +6845,7 @@
       <c r="J52" s="20"/>
       <c r="K52" s="59"/>
     </row>
-    <row r="53" spans="2:19" ht="62" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:19" ht="68" x14ac:dyDescent="0.2">
       <c r="D53" s="60" t="s">
         <v>215</v>
       </c>
@@ -6865,14 +6864,14 @@
       </c>
       <c r="J53" s="40"/>
       <c r="K53" s="59"/>
-      <c r="N53" s="78"/>
-      <c r="O53" s="78"/>
-      <c r="P53" s="78"/>
-      <c r="Q53" s="78"/>
-      <c r="R53" s="78"/>
-      <c r="S53" s="78"/>
-    </row>
-    <row r="54" spans="2:19" ht="62" x14ac:dyDescent="0.35">
+      <c r="N53" s="100"/>
+      <c r="O53" s="100"/>
+      <c r="P53" s="100"/>
+      <c r="Q53" s="100"/>
+      <c r="R53" s="100"/>
+      <c r="S53" s="100"/>
+    </row>
+    <row r="54" spans="2:19" ht="68" x14ac:dyDescent="0.2">
       <c r="D54" s="60" t="s">
         <v>218</v>
       </c>
@@ -6892,7 +6891,7 @@
       <c r="J54" s="20"/>
       <c r="K54" s="59"/>
     </row>
-    <row r="55" spans="2:19" ht="62" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:19" ht="68" x14ac:dyDescent="0.2">
       <c r="D55" s="60" t="s">
         <v>221</v>
       </c>
@@ -6912,32 +6911,32 @@
       <c r="J55" s="40"/>
       <c r="K55" s="59"/>
     </row>
-    <row r="56" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B56" s="79" t="s">
+    <row r="56" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B56" s="99" t="s">
         <v>228</v>
       </c>
-      <c r="C56" s="79"/>
-      <c r="D56" s="79"/>
-      <c r="E56" s="79"/>
-      <c r="F56" s="79"/>
-      <c r="G56" s="79"/>
-      <c r="H56" s="79"/>
-      <c r="I56" s="79"/>
-      <c r="J56" s="79"/>
-    </row>
-    <row r="57" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C57" s="81" t="s">
+      <c r="C56" s="99"/>
+      <c r="D56" s="99"/>
+      <c r="E56" s="99"/>
+      <c r="F56" s="99"/>
+      <c r="G56" s="99"/>
+      <c r="H56" s="99"/>
+      <c r="I56" s="99"/>
+      <c r="J56" s="99"/>
+    </row>
+    <row r="57" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="C57" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D57" s="81"/>
-      <c r="E57" s="81"/>
-      <c r="F57" s="81"/>
-      <c r="G57" s="81"/>
-      <c r="H57" s="81"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="81"/>
-    </row>
-    <row r="58" spans="2:19" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D57" s="98"/>
+      <c r="E57" s="98"/>
+      <c r="F57" s="98"/>
+      <c r="G57" s="98"/>
+      <c r="H57" s="98"/>
+      <c r="I57" s="98"/>
+      <c r="J57" s="98"/>
+    </row>
+    <row r="58" spans="2:19" ht="68" x14ac:dyDescent="0.2">
       <c r="D58" s="60" t="s">
         <v>229</v>
       </c>
@@ -6957,7 +6956,7 @@
       <c r="J58" s="20"/>
       <c r="K58" s="59"/>
     </row>
-    <row r="59" spans="2:19" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:19" ht="51" x14ac:dyDescent="0.2">
       <c r="D59" s="20" t="s">
         <v>232</v>
       </c>
@@ -6977,7 +6976,7 @@
       <c r="J59" s="40"/>
       <c r="K59" s="59"/>
     </row>
-    <row r="60" spans="2:19" ht="62" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:19" ht="68" x14ac:dyDescent="0.2">
       <c r="D60" s="60" t="s">
         <v>235</v>
       </c>
@@ -6997,7 +6996,7 @@
       <c r="J60" s="40"/>
       <c r="K60" s="59"/>
     </row>
-    <row r="61" spans="2:19" ht="62" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:19" ht="68" x14ac:dyDescent="0.2">
       <c r="D61" s="60" t="s">
         <v>229</v>
       </c>
@@ -7017,32 +7016,32 @@
       <c r="J61" s="40"/>
       <c r="K61" s="59"/>
     </row>
-    <row r="62" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B62" s="79" t="s">
+    <row r="62" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B62" s="99" t="s">
         <v>242</v>
       </c>
-      <c r="C62" s="79"/>
-      <c r="D62" s="79"/>
-      <c r="E62" s="79"/>
-      <c r="F62" s="79"/>
-      <c r="G62" s="79"/>
-      <c r="H62" s="79"/>
-      <c r="I62" s="79"/>
-      <c r="J62" s="79"/>
-    </row>
-    <row r="63" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C63" s="81" t="s">
+      <c r="C62" s="99"/>
+      <c r="D62" s="99"/>
+      <c r="E62" s="99"/>
+      <c r="F62" s="99"/>
+      <c r="G62" s="99"/>
+      <c r="H62" s="99"/>
+      <c r="I62" s="99"/>
+      <c r="J62" s="99"/>
+    </row>
+    <row r="63" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="C63" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D63" s="81"/>
-      <c r="E63" s="81"/>
-      <c r="F63" s="81"/>
-      <c r="G63" s="81"/>
-      <c r="H63" s="81"/>
-      <c r="I63" s="81"/>
-      <c r="J63" s="81"/>
-    </row>
-    <row r="64" spans="2:19" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D63" s="98"/>
+      <c r="E63" s="98"/>
+      <c r="F63" s="98"/>
+      <c r="G63" s="98"/>
+      <c r="H63" s="98"/>
+      <c r="I63" s="98"/>
+      <c r="J63" s="98"/>
+    </row>
+    <row r="64" spans="2:19" ht="85" x14ac:dyDescent="0.2">
       <c r="D64" s="20" t="s">
         <v>259</v>
       </c>
@@ -7062,7 +7061,7 @@
       <c r="J64" s="20"/>
       <c r="K64" s="59"/>
     </row>
-    <row r="65" spans="2:16" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" ht="85" x14ac:dyDescent="0.2">
       <c r="D65" s="20" t="s">
         <v>262</v>
       </c>
@@ -7082,7 +7081,7 @@
       <c r="J65" s="20"/>
       <c r="K65" s="59"/>
     </row>
-    <row r="66" spans="2:16" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="68" x14ac:dyDescent="0.2">
       <c r="D66" s="60" t="s">
         <v>265</v>
       </c>
@@ -7102,7 +7101,7 @@
       <c r="J66" s="20"/>
       <c r="K66" s="59"/>
     </row>
-    <row r="67" spans="2:16" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:16" ht="68" x14ac:dyDescent="0.2">
       <c r="D67" s="24" t="s">
         <v>255</v>
       </c>
@@ -7122,32 +7121,32 @@
       <c r="J67" s="20"/>
       <c r="K67" s="59"/>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B68" s="79" t="s">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B68" s="99" t="s">
         <v>268</v>
       </c>
-      <c r="C68" s="79"/>
-      <c r="D68" s="79"/>
-      <c r="E68" s="79"/>
-      <c r="F68" s="79"/>
-      <c r="G68" s="79"/>
-      <c r="H68" s="79"/>
-      <c r="I68" s="79"/>
-      <c r="J68" s="79"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C69" s="81" t="s">
+      <c r="C68" s="99"/>
+      <c r="D68" s="99"/>
+      <c r="E68" s="99"/>
+      <c r="F68" s="99"/>
+      <c r="G68" s="99"/>
+      <c r="H68" s="99"/>
+      <c r="I68" s="99"/>
+      <c r="J68" s="99"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C69" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D69" s="81"/>
-      <c r="E69" s="81"/>
-      <c r="F69" s="81"/>
-      <c r="G69" s="81"/>
-      <c r="H69" s="81"/>
-      <c r="I69" s="81"/>
-      <c r="J69" s="81"/>
-    </row>
-    <row r="70" spans="2:16" ht="62" x14ac:dyDescent="0.35">
+      <c r="D69" s="98"/>
+      <c r="E69" s="98"/>
+      <c r="F69" s="98"/>
+      <c r="G69" s="98"/>
+      <c r="H69" s="98"/>
+      <c r="I69" s="98"/>
+      <c r="J69" s="98"/>
+    </row>
+    <row r="70" spans="2:16" ht="68" x14ac:dyDescent="0.2">
       <c r="D70" s="61" t="s">
         <v>283</v>
       </c>
@@ -7165,7 +7164,7 @@
       <c r="J70" s="20"/>
       <c r="K70" s="59"/>
     </row>
-    <row r="71" spans="2:16" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:16" ht="68" x14ac:dyDescent="0.2">
       <c r="D71" s="32" t="s">
         <v>454</v>
       </c>
@@ -7182,12 +7181,12 @@
       <c r="I71" s="20"/>
       <c r="J71" s="20"/>
       <c r="K71" s="59"/>
-      <c r="M71" s="82"/>
-      <c r="N71" s="82"/>
-      <c r="O71" s="82"/>
-      <c r="P71" s="82"/>
-    </row>
-    <row r="72" spans="2:16" ht="62" x14ac:dyDescent="0.35">
+      <c r="M71" s="102"/>
+      <c r="N71" s="102"/>
+      <c r="O71" s="102"/>
+      <c r="P71" s="102"/>
+    </row>
+    <row r="72" spans="2:16" ht="68" x14ac:dyDescent="0.2">
       <c r="D72" s="32" t="s">
         <v>454</v>
       </c>
@@ -7209,7 +7208,7 @@
       <c r="O72" s="51"/>
       <c r="P72" s="51"/>
     </row>
-    <row r="73" spans="2:16" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:16" ht="68" x14ac:dyDescent="0.2">
       <c r="D73" s="32" t="s">
         <v>454</v>
       </c>
@@ -7227,32 +7226,32 @@
       <c r="J73" s="20"/>
       <c r="K73" s="59"/>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B74" s="79" t="s">
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B74" s="99" t="s">
         <v>288</v>
       </c>
-      <c r="C74" s="79"/>
-      <c r="D74" s="79"/>
-      <c r="E74" s="79"/>
-      <c r="F74" s="79"/>
-      <c r="G74" s="79"/>
-      <c r="H74" s="79"/>
-      <c r="I74" s="79"/>
-      <c r="J74" s="79"/>
-    </row>
-    <row r="75" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C75" s="81" t="s">
+      <c r="C74" s="99"/>
+      <c r="D74" s="99"/>
+      <c r="E74" s="99"/>
+      <c r="F74" s="99"/>
+      <c r="G74" s="99"/>
+      <c r="H74" s="99"/>
+      <c r="I74" s="99"/>
+      <c r="J74" s="99"/>
+    </row>
+    <row r="75" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C75" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D75" s="81"/>
-      <c r="E75" s="81"/>
-      <c r="F75" s="81"/>
-      <c r="G75" s="81"/>
-      <c r="H75" s="81"/>
-      <c r="I75" s="81"/>
-      <c r="J75" s="81"/>
-    </row>
-    <row r="76" spans="2:16" ht="78.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D75" s="98"/>
+      <c r="E75" s="98"/>
+      <c r="F75" s="98"/>
+      <c r="G75" s="98"/>
+      <c r="H75" s="98"/>
+      <c r="I75" s="98"/>
+      <c r="J75" s="98"/>
+    </row>
+    <row r="76" spans="2:16" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D76" s="34" t="s">
         <v>289</v>
       </c>
@@ -7272,7 +7271,7 @@
       <c r="J76" s="20"/>
       <c r="K76" s="59"/>
     </row>
-    <row r="77" spans="2:16" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:16" ht="85" x14ac:dyDescent="0.2">
       <c r="D77" s="63" t="s">
         <v>292</v>
       </c>
@@ -7292,7 +7291,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="59"/>
     </row>
-    <row r="78" spans="2:16" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:16" ht="68" x14ac:dyDescent="0.2">
       <c r="D78" s="34" t="s">
         <v>289</v>
       </c>
@@ -7312,7 +7311,7 @@
       <c r="J78" s="42"/>
       <c r="K78" s="59"/>
     </row>
-    <row r="79" spans="2:16" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:16" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D79" s="63" t="s">
         <v>297</v>
       </c>
@@ -7332,32 +7331,32 @@
       <c r="J79" s="42"/>
       <c r="K79" s="59"/>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B80" s="79" t="s">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B80" s="99" t="s">
         <v>302</v>
       </c>
-      <c r="C80" s="79"/>
-      <c r="D80" s="79"/>
-      <c r="E80" s="79"/>
-      <c r="F80" s="79"/>
-      <c r="G80" s="79"/>
-      <c r="H80" s="79"/>
-      <c r="I80" s="79"/>
-      <c r="J80" s="79"/>
-    </row>
-    <row r="81" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C81" s="81" t="s">
+      <c r="C80" s="99"/>
+      <c r="D80" s="99"/>
+      <c r="E80" s="99"/>
+      <c r="F80" s="99"/>
+      <c r="G80" s="99"/>
+      <c r="H80" s="99"/>
+      <c r="I80" s="99"/>
+      <c r="J80" s="99"/>
+    </row>
+    <row r="81" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C81" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D81" s="81"/>
-      <c r="E81" s="81"/>
-      <c r="F81" s="81"/>
-      <c r="G81" s="81"/>
-      <c r="H81" s="81"/>
-      <c r="I81" s="81"/>
-      <c r="J81" s="81"/>
-    </row>
-    <row r="82" spans="2:18" ht="62" x14ac:dyDescent="0.35">
+      <c r="D81" s="98"/>
+      <c r="E81" s="98"/>
+      <c r="F81" s="98"/>
+      <c r="G81" s="98"/>
+      <c r="H81" s="98"/>
+      <c r="I81" s="98"/>
+      <c r="J81" s="98"/>
+    </row>
+    <row r="82" spans="2:18" ht="68" x14ac:dyDescent="0.2">
       <c r="D82" s="20" t="s">
         <v>470</v>
       </c>
@@ -7377,7 +7376,7 @@
       <c r="J82" s="20"/>
       <c r="K82" s="59"/>
     </row>
-    <row r="83" spans="2:18" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:18" ht="85" x14ac:dyDescent="0.2">
       <c r="D83" s="34" t="s">
         <v>306</v>
       </c>
@@ -7397,7 +7396,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="59"/>
     </row>
-    <row r="84" spans="2:18" ht="114" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:18" ht="114" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D84" s="34" t="s">
         <v>306</v>
       </c>
@@ -7417,7 +7416,7 @@
       <c r="J84" s="42"/>
       <c r="K84" s="59"/>
     </row>
-    <row r="85" spans="2:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D85" s="63" t="s">
         <v>464</v>
       </c>
@@ -7437,32 +7436,32 @@
       <c r="J85" s="42"/>
       <c r="K85" s="59"/>
     </row>
-    <row r="86" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B86" s="79" t="s">
+    <row r="86" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B86" s="99" t="s">
         <v>319</v>
       </c>
-      <c r="C86" s="79"/>
-      <c r="D86" s="79"/>
-      <c r="E86" s="79"/>
-      <c r="F86" s="79"/>
-      <c r="G86" s="79"/>
-      <c r="H86" s="79"/>
-      <c r="I86" s="79"/>
-      <c r="J86" s="79"/>
-    </row>
-    <row r="87" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C87" s="81" t="s">
+      <c r="C86" s="99"/>
+      <c r="D86" s="99"/>
+      <c r="E86" s="99"/>
+      <c r="F86" s="99"/>
+      <c r="G86" s="99"/>
+      <c r="H86" s="99"/>
+      <c r="I86" s="99"/>
+      <c r="J86" s="99"/>
+    </row>
+    <row r="87" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C87" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D87" s="81"/>
-      <c r="E87" s="81"/>
-      <c r="F87" s="81"/>
-      <c r="G87" s="81"/>
-      <c r="H87" s="81"/>
-      <c r="I87" s="81"/>
-      <c r="J87" s="81"/>
-    </row>
-    <row r="88" spans="2:18" ht="93" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D87" s="98"/>
+      <c r="E87" s="98"/>
+      <c r="F87" s="98"/>
+      <c r="G87" s="98"/>
+      <c r="H87" s="98"/>
+      <c r="I87" s="98"/>
+      <c r="J87" s="98"/>
+    </row>
+    <row r="88" spans="2:18" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D88" s="61" t="s">
         <v>330</v>
       </c>
@@ -7482,7 +7481,7 @@
       <c r="J88" s="20"/>
       <c r="K88" s="59"/>
     </row>
-    <row r="89" spans="2:18" ht="78.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:18" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D89" s="61" t="s">
         <v>330</v>
       </c>
@@ -7501,13 +7500,13 @@
       </c>
       <c r="J89" s="29"/>
       <c r="K89" s="59"/>
-      <c r="N89" s="78"/>
-      <c r="O89" s="78"/>
-      <c r="P89" s="78"/>
-      <c r="Q89" s="78"/>
-      <c r="R89" s="78"/>
-    </row>
-    <row r="90" spans="2:18" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="N89" s="100"/>
+      <c r="O89" s="100"/>
+      <c r="P89" s="100"/>
+      <c r="Q89" s="100"/>
+      <c r="R89" s="100"/>
+    </row>
+    <row r="90" spans="2:18" ht="85" x14ac:dyDescent="0.2">
       <c r="D90" s="61" t="s">
         <v>334</v>
       </c>
@@ -7527,7 +7526,7 @@
       <c r="J90" s="42"/>
       <c r="K90" s="59"/>
     </row>
-    <row r="91" spans="2:18" ht="77.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:18" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D91" s="61" t="s">
         <v>323</v>
       </c>
@@ -7547,32 +7546,32 @@
       <c r="J91" s="42"/>
       <c r="K91" s="59"/>
     </row>
-    <row r="92" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B92" s="79" t="s">
+    <row r="92" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B92" s="99" t="s">
         <v>338</v>
       </c>
-      <c r="C92" s="79"/>
-      <c r="D92" s="79"/>
-      <c r="E92" s="79"/>
-      <c r="F92" s="79"/>
-      <c r="G92" s="79"/>
-      <c r="H92" s="79"/>
-      <c r="I92" s="79"/>
-      <c r="J92" s="79"/>
-    </row>
-    <row r="93" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C93" s="81" t="s">
+      <c r="C92" s="99"/>
+      <c r="D92" s="99"/>
+      <c r="E92" s="99"/>
+      <c r="F92" s="99"/>
+      <c r="G92" s="99"/>
+      <c r="H92" s="99"/>
+      <c r="I92" s="99"/>
+      <c r="J92" s="99"/>
+    </row>
+    <row r="93" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C93" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D93" s="81"/>
-      <c r="E93" s="81"/>
-      <c r="F93" s="81"/>
-      <c r="G93" s="81"/>
-      <c r="H93" s="81"/>
-      <c r="I93" s="81"/>
-      <c r="J93" s="81"/>
-    </row>
-    <row r="94" spans="2:18" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D93" s="98"/>
+      <c r="E93" s="98"/>
+      <c r="F93" s="98"/>
+      <c r="G93" s="98"/>
+      <c r="H93" s="98"/>
+      <c r="I93" s="98"/>
+      <c r="J93" s="98"/>
+    </row>
+    <row r="94" spans="2:18" ht="85" x14ac:dyDescent="0.2">
       <c r="D94" s="61" t="s">
         <v>342</v>
       </c>
@@ -7592,7 +7591,7 @@
       <c r="J94" s="20"/>
       <c r="K94" s="59"/>
     </row>
-    <row r="95" spans="2:18" ht="62" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:18" ht="51" x14ac:dyDescent="0.2">
       <c r="D95" s="61" t="s">
         <v>342</v>
       </c>
@@ -7612,7 +7611,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="59"/>
     </row>
-    <row r="96" spans="2:18" ht="62" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:18" ht="68" x14ac:dyDescent="0.2">
       <c r="D96" s="32" t="s">
         <v>339</v>
       </c>
@@ -7632,7 +7631,7 @@
       <c r="J96" s="42"/>
       <c r="K96" s="59"/>
     </row>
-    <row r="97" spans="2:11" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:11" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D97" s="61" t="s">
         <v>350</v>
       </c>
@@ -7652,32 +7651,32 @@
       <c r="J97" s="42"/>
       <c r="K97" s="59"/>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B98" s="79" t="s">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B98" s="99" t="s">
         <v>357</v>
       </c>
-      <c r="C98" s="79"/>
-      <c r="D98" s="79"/>
-      <c r="E98" s="79"/>
-      <c r="F98" s="79"/>
-      <c r="G98" s="79"/>
-      <c r="H98" s="79"/>
-      <c r="I98" s="79"/>
-      <c r="J98" s="79"/>
-    </row>
-    <row r="99" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="81" t="s">
+      <c r="C98" s="99"/>
+      <c r="D98" s="99"/>
+      <c r="E98" s="99"/>
+      <c r="F98" s="99"/>
+      <c r="G98" s="99"/>
+      <c r="H98" s="99"/>
+      <c r="I98" s="99"/>
+      <c r="J98" s="99"/>
+    </row>
+    <row r="99" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C99" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D99" s="81"/>
-      <c r="E99" s="81"/>
-      <c r="F99" s="81"/>
-      <c r="G99" s="81"/>
-      <c r="H99" s="81"/>
-      <c r="I99" s="81"/>
-      <c r="J99" s="81"/>
-    </row>
-    <row r="100" spans="2:11" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="D99" s="98"/>
+      <c r="E99" s="98"/>
+      <c r="F99" s="98"/>
+      <c r="G99" s="98"/>
+      <c r="H99" s="98"/>
+      <c r="I99" s="98"/>
+      <c r="J99" s="98"/>
+    </row>
+    <row r="100" spans="2:11" ht="119" x14ac:dyDescent="0.2">
       <c r="D100" s="24" t="s">
         <v>363</v>
       </c>
@@ -7697,7 +7696,7 @@
       <c r="J100" s="20"/>
       <c r="K100" s="59"/>
     </row>
-    <row r="101" spans="2:11" ht="93" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:11" ht="102" x14ac:dyDescent="0.2">
       <c r="D101" s="24" t="s">
         <v>360</v>
       </c>
@@ -7717,7 +7716,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="59"/>
     </row>
-    <row r="102" spans="2:11" ht="93" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:11" ht="85" x14ac:dyDescent="0.2">
       <c r="D102" s="28" t="s">
         <v>371</v>
       </c>
@@ -7737,7 +7736,7 @@
       <c r="J102" s="42"/>
       <c r="K102" s="59"/>
     </row>
-    <row r="103" spans="2:11" ht="81.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:11" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D103" s="24" t="s">
         <v>374</v>
       </c>
@@ -7759,12 +7758,30 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="C33:J33"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="C45:J45"/>
-    <mergeCell ref="C39:J39"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="M28:T28"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="P37:T37"/>
+    <mergeCell ref="B92:J92"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="C63:J63"/>
+    <mergeCell ref="N53:S53"/>
+    <mergeCell ref="M71:P71"/>
+    <mergeCell ref="N89:R89"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="N47:Q47"/>
+    <mergeCell ref="N49:S49"/>
+    <mergeCell ref="C93:J93"/>
+    <mergeCell ref="B98:J98"/>
+    <mergeCell ref="C99:J99"/>
+    <mergeCell ref="C75:J75"/>
+    <mergeCell ref="B74:J74"/>
+    <mergeCell ref="B80:J80"/>
+    <mergeCell ref="C81:J81"/>
+    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="C87:J87"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B38:J38"/>
     <mergeCell ref="C69:J69"/>
@@ -7781,30 +7798,12 @@
     <mergeCell ref="B56:J56"/>
     <mergeCell ref="C57:J57"/>
     <mergeCell ref="B62:J62"/>
-    <mergeCell ref="C93:J93"/>
-    <mergeCell ref="B98:J98"/>
-    <mergeCell ref="C99:J99"/>
-    <mergeCell ref="C75:J75"/>
-    <mergeCell ref="B74:J74"/>
-    <mergeCell ref="B80:J80"/>
-    <mergeCell ref="C81:J81"/>
-    <mergeCell ref="B86:J86"/>
-    <mergeCell ref="C87:J87"/>
-    <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="M28:T28"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="P37:T37"/>
-    <mergeCell ref="B92:J92"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="B68:J68"/>
-    <mergeCell ref="C63:J63"/>
-    <mergeCell ref="N53:S53"/>
-    <mergeCell ref="M71:P71"/>
-    <mergeCell ref="N89:R89"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="N47:Q47"/>
-    <mergeCell ref="N49:S49"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="C45:J45"/>
+    <mergeCell ref="C39:J39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -7825,25 +7824,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CA40C9-0910-4F15-B410-B91452662D95}">
-  <dimension ref="A1:M103"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L103"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="48.1796875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="48.1796875" style="13" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="34.1796875" style="13" customWidth="1"/>
-    <col min="7" max="7" width="61.453125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="48.1640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="48.1640625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" style="14" customWidth="1"/>
+    <col min="6" max="6" width="34.1640625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="61.5" style="13" customWidth="1"/>
     <col min="8" max="8" width="44" style="13" customWidth="1"/>
-    <col min="9" max="9" width="41.81640625" style="13" customWidth="1"/>
-    <col min="10" max="10" width="33.81640625" style="13" customWidth="1"/>
-    <col min="11" max="11" width="9.26953125" customWidth="1"/>
-    <col min="12" max="12" width="30" style="10" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="8.54296875" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="9" max="9" width="41.83203125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="33.83203125" style="13" customWidth="1"/>
+    <col min="11" max="11" width="30" style="10" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:11" s="3" customFormat="1" ht="34" x14ac:dyDescent="0.25">
       <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
@@ -7871,41 +7869,36 @@
       <c r="J1" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="44" t="s">
-        <v>393</v>
-      </c>
-      <c r="L1" s="38" t="s">
+      <c r="K1" s="38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="76" t="s">
+    <row r="2" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B2" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="39"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C3" s="77" t="s">
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C3" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="39"/>
-    </row>
-    <row r="4" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+    </row>
+    <row r="4" spans="2:11" ht="85" x14ac:dyDescent="0.2">
       <c r="D4" s="39" t="s">
         <v>551</v>
       </c>
@@ -7925,10 +7918,9 @@
       <c r="J4" s="13" t="s">
         <v>555</v>
       </c>
-      <c r="K4" s="59"/>
-      <c r="L4" s="17"/>
-    </row>
-    <row r="5" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="K4" s="17"/>
+    </row>
+    <row r="5" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="D5" s="39" t="s">
         <v>556</v>
       </c>
@@ -7948,10 +7940,9 @@
       <c r="J5" s="13" t="s">
         <v>560</v>
       </c>
-      <c r="K5" s="59"/>
-      <c r="L5" s="17"/>
-    </row>
-    <row r="6" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="K5" s="17"/>
+    </row>
+    <row r="6" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="C6" s="6" t="s">
         <v>21</v>
       </c>
@@ -7974,9 +7965,8 @@
       <c r="J6" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="K6" s="59"/>
-    </row>
-    <row r="7" spans="2:12" ht="46.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="2:11" ht="51" x14ac:dyDescent="0.2">
       <c r="C7" s="6"/>
       <c r="D7" s="39" t="s">
         <v>564</v>
@@ -7997,34 +7987,33 @@
       <c r="J7" s="13" t="s">
         <v>568</v>
       </c>
-      <c r="K7" s="59"/>
-    </row>
-    <row r="8" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="76" t="s">
+    </row>
+    <row r="8" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B8" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="76"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C9" s="77" t="s">
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="103"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C9" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-    </row>
-    <row r="10" spans="2:12" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="104"/>
+    </row>
+    <row r="10" spans="2:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="39" t="s">
@@ -8046,9 +8035,8 @@
       <c r="J10" s="13" t="s">
         <v>573</v>
       </c>
-      <c r="K10" s="59"/>
-    </row>
-    <row r="11" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
       <c r="D11" s="39" t="s">
@@ -8070,9 +8058,8 @@
       <c r="J11" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="K11" s="59"/>
-    </row>
-    <row r="12" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="39" t="s">
@@ -8094,9 +8081,8 @@
       <c r="J12" s="13" t="s">
         <v>583</v>
       </c>
-      <c r="K12" s="59"/>
-    </row>
-    <row r="13" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="39" t="s">
@@ -8118,34 +8104,33 @@
       <c r="J13" s="13" t="s">
         <v>587</v>
       </c>
-      <c r="K13" s="59"/>
-    </row>
-    <row r="14" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="76" t="s">
+    </row>
+    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B14" s="103" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="77" t="s">
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="103"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C15" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
-    </row>
-    <row r="16" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="104"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="104"/>
+    </row>
+    <row r="16" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="39" t="s">
@@ -8167,10 +8152,9 @@
       <c r="J16" s="13" t="s">
         <v>593</v>
       </c>
-      <c r="K16" s="59"/>
-      <c r="L16" s="15"/>
-    </row>
-    <row r="17" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="K16" s="15"/>
+    </row>
+    <row r="17" spans="2:11" ht="51" x14ac:dyDescent="0.2">
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
       <c r="D17" s="39" t="s">
@@ -8192,10 +8176,9 @@
       <c r="J17" s="13" t="s">
         <v>598</v>
       </c>
-      <c r="K17" s="59"/>
-      <c r="L17" s="15"/>
-    </row>
-    <row r="18" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="K17" s="15"/>
+    </row>
+    <row r="18" spans="2:11" ht="51" x14ac:dyDescent="0.2">
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
       <c r="D18" s="39" t="s">
@@ -8217,10 +8200,9 @@
       <c r="J18" s="13" t="s">
         <v>603</v>
       </c>
-      <c r="K18" s="59"/>
-      <c r="L18" s="11"/>
-    </row>
-    <row r="19" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="K18" s="11"/>
+    </row>
+    <row r="19" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
       <c r="D19" s="39" t="s">
@@ -8242,35 +8224,34 @@
       <c r="J19" s="13" t="s">
         <v>608</v>
       </c>
-      <c r="K19" s="59"/>
-      <c r="L19" s="12"/>
-    </row>
-    <row r="20" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="76" t="s">
+      <c r="K19" s="12"/>
+    </row>
+    <row r="20" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B20" s="103" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="76"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="76"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="77" t="s">
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="103"/>
+      <c r="J20" s="103"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C21" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-    </row>
-    <row r="22" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="104"/>
+    </row>
+    <row r="22" spans="2:11" ht="85" x14ac:dyDescent="0.2">
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
       <c r="D22" s="20" t="s">
@@ -8292,10 +8273,9 @@
       <c r="J22" s="20" t="s">
         <v>611</v>
       </c>
-      <c r="K22" s="59"/>
-      <c r="L22" s="15"/>
-    </row>
-    <row r="23" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="K22" s="15"/>
+    </row>
+    <row r="23" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
       <c r="D23" s="20" t="s">
@@ -8317,10 +8297,9 @@
       <c r="J23" s="20" t="s">
         <v>614</v>
       </c>
-      <c r="K23" s="59"/>
-      <c r="L23" s="15"/>
-    </row>
-    <row r="24" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="K23" s="15"/>
+    </row>
+    <row r="24" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
       <c r="D24" s="20" t="s">
@@ -8342,10 +8321,9 @@
       <c r="J24" s="20" t="s">
         <v>618</v>
       </c>
-      <c r="K24" s="59"/>
-      <c r="L24" s="11"/>
-    </row>
-    <row r="25" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="K24" s="11"/>
+    </row>
+    <row r="25" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
       <c r="D25" s="20" t="s">
@@ -8367,35 +8345,34 @@
       <c r="J25" s="20" t="s">
         <v>621</v>
       </c>
-      <c r="K25" s="59"/>
-      <c r="L25" s="12"/>
-    </row>
-    <row r="26" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="76" t="s">
+      <c r="K25" s="12"/>
+    </row>
+    <row r="26" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B26" s="103" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
-      <c r="I26" s="76"/>
-      <c r="J26" s="76"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="77" t="s">
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="103"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C27" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-    </row>
-    <row r="28" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="104"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="104"/>
+    </row>
+    <row r="28" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="D28" s="19" t="s">
         <v>625</v>
       </c>
@@ -8415,12 +8392,11 @@
       <c r="J28" s="19" t="s">
         <v>628</v>
       </c>
-      <c r="K28" s="59"/>
-      <c r="L28" s="15" t="s">
+      <c r="K28" s="15" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="D29" s="13" t="s">
         <v>629</v>
       </c>
@@ -8440,12 +8416,11 @@
       <c r="J29" s="19" t="s">
         <v>632</v>
       </c>
-      <c r="K29" s="59"/>
-      <c r="L29" s="15" t="s">
+      <c r="K29" s="15" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:11" ht="51" x14ac:dyDescent="0.2">
       <c r="D30" s="13" t="s">
         <v>633</v>
       </c>
@@ -8464,12 +8439,11 @@
       <c r="J30" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="K30" s="59"/>
-      <c r="L30" s="12" t="s">
+      <c r="K30" s="12" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="D31" s="13" t="s">
         <v>638</v>
       </c>
@@ -8488,35 +8462,34 @@
       <c r="J31" s="13" t="s">
         <v>642</v>
       </c>
-      <c r="K31" s="59"/>
-      <c r="L31" s="12"/>
-    </row>
-    <row r="32" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="76" t="s">
+      <c r="K31" s="12"/>
+    </row>
+    <row r="32" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B32" s="103" t="s">
         <v>809</v>
       </c>
-      <c r="C32" s="76"/>
-      <c r="D32" s="76"/>
-      <c r="E32" s="76"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-      <c r="I32" s="76"/>
-      <c r="J32" s="76"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="C33" s="77" t="s">
+      <c r="C32" s="103"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103"/>
+      <c r="F32" s="103"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="103"/>
+      <c r="J32" s="103"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C33" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77"/>
-      <c r="J33" s="77"/>
-    </row>
-    <row r="34" spans="2:13" ht="62" x14ac:dyDescent="0.35">
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="104"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="104"/>
+    </row>
+    <row r="34" spans="2:12" ht="68" x14ac:dyDescent="0.2">
       <c r="D34" s="20" t="s">
         <v>645</v>
       </c>
@@ -8536,10 +8509,9 @@
       <c r="J34" s="20" t="s">
         <v>649</v>
       </c>
-      <c r="K34" s="59"/>
-      <c r="L34" s="17"/>
-    </row>
-    <row r="35" spans="2:13" ht="62" x14ac:dyDescent="0.35">
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" spans="2:12" ht="68" x14ac:dyDescent="0.2">
       <c r="D35" s="20" t="s">
         <v>650</v>
       </c>
@@ -8559,9 +8531,8 @@
       <c r="J35" s="20" t="s">
         <v>654</v>
       </c>
-      <c r="K35" s="59"/>
-    </row>
-    <row r="36" spans="2:13" ht="46.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="2:12" ht="51" x14ac:dyDescent="0.2">
       <c r="D36" s="20" t="s">
         <v>655</v>
       </c>
@@ -8581,12 +8552,11 @@
       <c r="J36" s="20" t="s">
         <v>658</v>
       </c>
-      <c r="K36" s="59"/>
-      <c r="L36" s="11" t="s">
+      <c r="K36" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="62" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:12" ht="51" x14ac:dyDescent="0.2">
       <c r="D37" s="20" t="s">
         <v>659</v>
       </c>
@@ -8606,38 +8576,37 @@
       <c r="J37" s="20" t="s">
         <v>663</v>
       </c>
-      <c r="K37" s="59"/>
-      <c r="L37" s="12" t="s">
+      <c r="K37" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="2:13" s="4" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="76" t="s">
+    <row r="38" spans="2:12" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="B38" s="103" t="s">
         <v>143</v>
       </c>
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
-      <c r="I38" s="76"/>
-      <c r="J38" s="76"/>
-      <c r="L38" s="9"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="C39" s="77" t="s">
+      <c r="C38" s="103"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="103"/>
+      <c r="F38" s="103"/>
+      <c r="G38" s="103"/>
+      <c r="H38" s="103"/>
+      <c r="I38" s="103"/>
+      <c r="J38" s="103"/>
+      <c r="K38" s="9"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C39" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="77"/>
-      <c r="J39" s="77"/>
-    </row>
-    <row r="40" spans="2:13" ht="62" x14ac:dyDescent="0.35">
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="104"/>
+      <c r="G39" s="104"/>
+      <c r="H39" s="104"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="104"/>
+    </row>
+    <row r="40" spans="2:12" ht="68" x14ac:dyDescent="0.2">
       <c r="B40" s="21"/>
       <c r="C40" s="22" t="s">
         <v>144</v>
@@ -8661,10 +8630,9 @@
       <c r="J40" s="20" t="s">
         <v>669</v>
       </c>
-      <c r="K40" s="59"/>
-      <c r="L40" s="15"/>
-    </row>
-    <row r="41" spans="2:13" ht="62" x14ac:dyDescent="0.35">
+      <c r="K40" s="15"/>
+    </row>
+    <row r="41" spans="2:12" ht="51" x14ac:dyDescent="0.2">
       <c r="B41" s="21"/>
       <c r="C41" s="23" t="s">
         <v>150</v>
@@ -8688,13 +8656,12 @@
       <c r="J41" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="K41" s="59"/>
-      <c r="L41" s="8" t="s">
+      <c r="K41" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="M41" s="5"/>
-    </row>
-    <row r="42" spans="2:13" ht="84" x14ac:dyDescent="0.35">
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="2:12" ht="90" x14ac:dyDescent="0.2">
       <c r="B42" s="21"/>
       <c r="C42" s="5" t="s">
         <v>155</v>
@@ -8718,12 +8685,11 @@
       <c r="J42" s="20" t="s">
         <v>678</v>
       </c>
-      <c r="K42" s="59"/>
-      <c r="L42" s="8" t="s">
+      <c r="K42" s="8" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="21"/>
       <c r="C43" s="5"/>
       <c r="D43" s="20" t="s">
@@ -8745,35 +8711,34 @@
       <c r="J43" s="20" t="s">
         <v>683</v>
       </c>
-      <c r="K43" s="59"/>
-      <c r="L43" s="8"/>
-    </row>
-    <row r="44" spans="2:13" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="76" t="s">
+      <c r="K43" s="8"/>
+    </row>
+    <row r="44" spans="2:12" ht="24" x14ac:dyDescent="0.3">
+      <c r="B44" s="103" t="s">
         <v>178</v>
       </c>
-      <c r="C44" s="76"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="76"/>
-      <c r="I44" s="76"/>
-      <c r="J44" s="76"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="C45" s="77" t="s">
+      <c r="C44" s="103"/>
+      <c r="D44" s="103"/>
+      <c r="E44" s="103"/>
+      <c r="F44" s="103"/>
+      <c r="G44" s="103"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="103"/>
+      <c r="J44" s="103"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C45" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="77"/>
-      <c r="G45" s="77"/>
-      <c r="H45" s="77"/>
-      <c r="I45" s="77"/>
-      <c r="J45" s="77"/>
-    </row>
-    <row r="46" spans="2:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="D45" s="104"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="104"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="104"/>
+    </row>
+    <row r="46" spans="2:12" ht="91" x14ac:dyDescent="0.2">
       <c r="C46" s="16" t="s">
         <v>179</v>
       </c>
@@ -8796,10 +8761,9 @@
       <c r="J46" s="20" t="s">
         <v>687</v>
       </c>
-      <c r="K46" s="59"/>
-      <c r="L46" s="17"/>
-    </row>
-    <row r="47" spans="2:13" ht="98.5" x14ac:dyDescent="0.35">
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="2:12" ht="106" x14ac:dyDescent="0.2">
       <c r="C47" s="16" t="s">
         <v>184</v>
       </c>
@@ -8822,10 +8786,9 @@
       <c r="J47" s="20" t="s">
         <v>691</v>
       </c>
-      <c r="K47" s="59"/>
-      <c r="L47" s="17"/>
-    </row>
-    <row r="48" spans="2:13" ht="78.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="2:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C48" s="6" t="s">
         <v>189</v>
       </c>
@@ -8848,9 +8811,8 @@
       <c r="J48" s="20" t="s">
         <v>696</v>
       </c>
-      <c r="K48" s="59"/>
-    </row>
-    <row r="49" spans="2:12" ht="70.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="2:11" ht="76" x14ac:dyDescent="0.2">
       <c r="C49" s="6" t="s">
         <v>194</v>
       </c>
@@ -8873,37 +8835,36 @@
       <c r="J49" s="20" t="s">
         <v>700</v>
       </c>
-      <c r="K49" s="59"/>
-      <c r="L49" s="11" t="s">
+      <c r="K49" s="11" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="76" t="s">
+    <row r="50" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B50" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="C50" s="76"/>
-      <c r="D50" s="76"/>
-      <c r="E50" s="76"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="76"/>
-      <c r="H50" s="76"/>
-      <c r="I50" s="76"/>
-      <c r="J50" s="76"/>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C51" s="77" t="s">
+      <c r="C50" s="103"/>
+      <c r="D50" s="103"/>
+      <c r="E50" s="103"/>
+      <c r="F50" s="103"/>
+      <c r="G50" s="103"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="103"/>
+      <c r="J50" s="103"/>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C51" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D51" s="77"/>
-      <c r="E51" s="77"/>
-      <c r="F51" s="77"/>
-      <c r="G51" s="77"/>
-      <c r="H51" s="77"/>
-      <c r="I51" s="77"/>
-      <c r="J51" s="77"/>
-    </row>
-    <row r="52" spans="2:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="D51" s="104"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="104"/>
+      <c r="G51" s="104"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="104"/>
+    </row>
+    <row r="52" spans="2:11" ht="51" x14ac:dyDescent="0.2">
       <c r="D52" s="19" t="s">
         <v>704</v>
       </c>
@@ -8923,9 +8884,8 @@
       <c r="J52" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="K52" s="59"/>
-    </row>
-    <row r="53" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="D53" s="19" t="s">
         <v>708</v>
       </c>
@@ -8942,12 +8902,11 @@
       <c r="I53" s="19" t="s">
         <v>711</v>
       </c>
-      <c r="J53" s="90" t="s">
+      <c r="J53" s="76" t="s">
         <v>721</v>
       </c>
-      <c r="K53" s="59"/>
-    </row>
-    <row r="54" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="D54" s="19" t="s">
         <v>712</v>
       </c>
@@ -8967,9 +8926,8 @@
       <c r="J54" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="K54" s="59"/>
-    </row>
-    <row r="55" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="D55" s="19" t="s">
         <v>716</v>
       </c>
@@ -8986,37 +8944,36 @@
       <c r="I55" s="18" t="s">
         <v>719</v>
       </c>
-      <c r="J55" s="90" t="s">
+      <c r="J55" s="76" t="s">
         <v>723</v>
       </c>
-      <c r="K55" s="59"/>
-    </row>
-    <row r="56" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="76" t="s">
+    </row>
+    <row r="56" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B56" s="103" t="s">
         <v>228</v>
       </c>
-      <c r="C56" s="76"/>
-      <c r="D56" s="76"/>
-      <c r="E56" s="76"/>
-      <c r="F56" s="76"/>
-      <c r="G56" s="76"/>
-      <c r="H56" s="76"/>
-      <c r="I56" s="76"/>
-      <c r="J56" s="76"/>
-    </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C57" s="77" t="s">
+      <c r="C56" s="103"/>
+      <c r="D56" s="103"/>
+      <c r="E56" s="103"/>
+      <c r="F56" s="103"/>
+      <c r="G56" s="103"/>
+      <c r="H56" s="103"/>
+      <c r="I56" s="103"/>
+      <c r="J56" s="103"/>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C57" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D57" s="77"/>
-      <c r="E57" s="77"/>
-      <c r="F57" s="77"/>
-      <c r="G57" s="77"/>
-      <c r="H57" s="77"/>
-      <c r="I57" s="77"/>
-      <c r="J57" s="77"/>
-    </row>
-    <row r="58" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="D57" s="104"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="104"/>
+      <c r="G57" s="104"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="104"/>
+    </row>
+    <row r="58" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="D58" s="20" t="s">
         <v>724</v>
       </c>
@@ -9036,9 +8993,8 @@
       <c r="J58" s="20" t="s">
         <v>737</v>
       </c>
-      <c r="K58" s="59"/>
-    </row>
-    <row r="59" spans="2:12" ht="77.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="2:11" ht="85" x14ac:dyDescent="0.2">
       <c r="D59" s="20" t="s">
         <v>727</v>
       </c>
@@ -9058,9 +9014,8 @@
       <c r="J59" s="20" t="s">
         <v>738</v>
       </c>
-      <c r="K59" s="59"/>
-    </row>
-    <row r="60" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="D60" s="20" t="s">
         <v>730</v>
       </c>
@@ -9080,9 +9035,8 @@
       <c r="J60" s="20" t="s">
         <v>739</v>
       </c>
-      <c r="K60" s="59"/>
-    </row>
-    <row r="61" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="D61" s="20" t="s">
         <v>733</v>
       </c>
@@ -9102,34 +9056,33 @@
       <c r="J61" s="20" t="s">
         <v>740</v>
       </c>
-      <c r="K61" s="59"/>
-    </row>
-    <row r="62" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="76" t="s">
+    </row>
+    <row r="62" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B62" s="103" t="s">
         <v>242</v>
       </c>
-      <c r="C62" s="76"/>
-      <c r="D62" s="76"/>
-      <c r="E62" s="76"/>
-      <c r="F62" s="76"/>
-      <c r="G62" s="76"/>
-      <c r="H62" s="76"/>
-      <c r="I62" s="76"/>
-      <c r="J62" s="76"/>
-    </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C63" s="77" t="s">
+      <c r="C62" s="103"/>
+      <c r="D62" s="103"/>
+      <c r="E62" s="103"/>
+      <c r="F62" s="103"/>
+      <c r="G62" s="103"/>
+      <c r="H62" s="103"/>
+      <c r="I62" s="103"/>
+      <c r="J62" s="103"/>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C63" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D63" s="77"/>
-      <c r="E63" s="77"/>
-      <c r="F63" s="77"/>
-      <c r="G63" s="77"/>
-      <c r="H63" s="77"/>
-      <c r="I63" s="77"/>
-      <c r="J63" s="77"/>
-    </row>
-    <row r="64" spans="2:12" s="18" customFormat="1" ht="62" x14ac:dyDescent="0.35">
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="104"/>
+      <c r="G63" s="104"/>
+      <c r="H63" s="104"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="104"/>
+    </row>
+    <row r="64" spans="2:11" s="18" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="D64" s="20" t="s">
         <v>744</v>
       </c>
@@ -9149,9 +9102,8 @@
       <c r="J64" s="20" t="s">
         <v>747</v>
       </c>
-      <c r="K64" s="59"/>
-    </row>
-    <row r="65" spans="1:12" s="18" customFormat="1" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:11" s="18" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="D65" s="20" t="s">
         <v>748</v>
       </c>
@@ -9171,9 +9123,8 @@
       <c r="J65" s="20" t="s">
         <v>760</v>
       </c>
-      <c r="K65" s="59"/>
-    </row>
-    <row r="66" spans="1:12" s="18" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:11" s="18" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="D66" s="20" t="s">
         <v>752</v>
       </c>
@@ -9193,9 +9144,8 @@
       <c r="J66" s="20" t="s">
         <v>755</v>
       </c>
-      <c r="K66" s="59"/>
-    </row>
-    <row r="67" spans="1:12" s="18" customFormat="1" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:11" s="18" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="D67" s="20" t="s">
         <v>756</v>
       </c>
@@ -9215,34 +9165,33 @@
       <c r="J67" s="20" t="s">
         <v>759</v>
       </c>
-      <c r="K67" s="59"/>
-    </row>
-    <row r="68" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="76" t="s">
+    </row>
+    <row r="68" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B68" s="103" t="s">
         <v>268</v>
       </c>
-      <c r="C68" s="76"/>
-      <c r="D68" s="76"/>
-      <c r="E68" s="76"/>
-      <c r="F68" s="76"/>
-      <c r="G68" s="76"/>
-      <c r="H68" s="76"/>
-      <c r="I68" s="76"/>
-      <c r="J68" s="76"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C69" s="77" t="s">
+      <c r="C68" s="103"/>
+      <c r="D68" s="103"/>
+      <c r="E68" s="103"/>
+      <c r="F68" s="103"/>
+      <c r="G68" s="103"/>
+      <c r="H68" s="103"/>
+      <c r="I68" s="103"/>
+      <c r="J68" s="103"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C69" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D69" s="77"/>
-      <c r="E69" s="77"/>
-      <c r="F69" s="77"/>
-      <c r="G69" s="77"/>
-      <c r="H69" s="77"/>
-      <c r="I69" s="77"/>
-      <c r="J69" s="77"/>
-    </row>
-    <row r="70" spans="1:12" s="96" customFormat="1" ht="62" x14ac:dyDescent="0.35">
+      <c r="D69" s="104"/>
+      <c r="E69" s="104"/>
+      <c r="F69" s="104"/>
+      <c r="G69" s="104"/>
+      <c r="H69" s="104"/>
+      <c r="I69" s="104"/>
+      <c r="J69" s="104"/>
+    </row>
+    <row r="70" spans="1:11" s="81" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="D70" s="33" t="s">
         <v>764</v>
       </c>
@@ -9255,18 +9204,17 @@
       <c r="G70" s="33" t="s">
         <v>766</v>
       </c>
-      <c r="H70" s="92"/>
+      <c r="H70" s="78"/>
       <c r="I70" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="J70" s="92" t="s">
+      <c r="J70" s="78" t="s">
         <v>783</v>
       </c>
-      <c r="K70" s="94"/>
-      <c r="L70" s="97"/>
-    </row>
-    <row r="71" spans="1:12" s="95" customFormat="1" ht="93" x14ac:dyDescent="0.35">
-      <c r="D71" s="98" t="s">
+      <c r="K70" s="82"/>
+    </row>
+    <row r="71" spans="1:11" s="80" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+      <c r="D71" s="83" t="s">
         <v>768</v>
       </c>
       <c r="E71" s="33" t="s">
@@ -9275,21 +9223,20 @@
       <c r="F71" s="33" t="s">
         <v>769</v>
       </c>
-      <c r="G71" s="98" t="s">
+      <c r="G71" s="83" t="s">
         <v>770</v>
       </c>
-      <c r="H71" s="92"/>
+      <c r="H71" s="78"/>
       <c r="I71" s="34" t="s">
         <v>771</v>
       </c>
-      <c r="J71" s="92" t="s">
+      <c r="J71" s="78" t="s">
         <v>780</v>
       </c>
-      <c r="K71" s="94"/>
-      <c r="L71" s="99"/>
-    </row>
-    <row r="72" spans="1:12" s="95" customFormat="1" ht="62" x14ac:dyDescent="0.35">
-      <c r="D72" s="98" t="s">
+      <c r="K71" s="84"/>
+    </row>
+    <row r="72" spans="1:11" s="80" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+      <c r="D72" s="83" t="s">
         <v>772</v>
       </c>
       <c r="E72" s="33" t="s">
@@ -9298,21 +9245,20 @@
       <c r="F72" s="33" t="s">
         <v>773</v>
       </c>
-      <c r="G72" s="98" t="s">
+      <c r="G72" s="83" t="s">
         <v>774</v>
       </c>
-      <c r="H72" s="92"/>
+      <c r="H72" s="78"/>
       <c r="I72" s="34" t="s">
         <v>775</v>
       </c>
       <c r="J72" s="34" t="s">
         <v>781</v>
       </c>
-      <c r="K72" s="94"/>
-      <c r="L72" s="99"/>
-    </row>
-    <row r="73" spans="1:12" s="95" customFormat="1" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="D73" s="98" t="s">
+      <c r="K72" s="84"/>
+    </row>
+    <row r="73" spans="1:11" s="80" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="D73" s="83" t="s">
         <v>776</v>
       </c>
       <c r="E73" s="33" t="s">
@@ -9321,78 +9267,76 @@
       <c r="F73" s="33" t="s">
         <v>777</v>
       </c>
-      <c r="G73" s="98" t="s">
+      <c r="G73" s="83" t="s">
         <v>778</v>
       </c>
-      <c r="H73" s="92"/>
-      <c r="I73" s="92" t="s">
+      <c r="H73" s="78"/>
+      <c r="I73" s="78" t="s">
         <v>779</v>
       </c>
-      <c r="J73" s="92" t="s">
+      <c r="J73" s="78" t="s">
         <v>782</v>
       </c>
-      <c r="K73" s="94"/>
-      <c r="L73" s="99"/>
-    </row>
-    <row r="74" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="76" t="s">
+      <c r="K73" s="84"/>
+    </row>
+    <row r="74" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B74" s="103" t="s">
         <v>288</v>
       </c>
-      <c r="C74" s="76"/>
-      <c r="D74" s="76"/>
-      <c r="E74" s="76"/>
-      <c r="F74" s="76"/>
-      <c r="G74" s="76"/>
-      <c r="H74" s="76"/>
-      <c r="I74" s="76"/>
-      <c r="J74" s="76"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C75" s="77" t="s">
+      <c r="C74" s="103"/>
+      <c r="D74" s="103"/>
+      <c r="E74" s="103"/>
+      <c r="F74" s="103"/>
+      <c r="G74" s="103"/>
+      <c r="H74" s="103"/>
+      <c r="I74" s="103"/>
+      <c r="J74" s="103"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C75" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="77"/>
-      <c r="E75" s="77"/>
-      <c r="F75" s="77"/>
-      <c r="G75" s="77"/>
-      <c r="H75" s="77"/>
-      <c r="I75" s="77"/>
-      <c r="J75" s="77"/>
-    </row>
-    <row r="76" spans="1:12" s="95" customFormat="1" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A76" s="91"/>
-      <c r="B76" s="91"/>
-      <c r="C76" s="91"/>
+      <c r="D75" s="104"/>
+      <c r="E75" s="104"/>
+      <c r="F75" s="104"/>
+      <c r="G75" s="104"/>
+      <c r="H75" s="104"/>
+      <c r="I75" s="104"/>
+      <c r="J75" s="104"/>
+    </row>
+    <row r="76" spans="1:11" s="80" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+      <c r="A76" s="77"/>
+      <c r="B76" s="77"/>
+      <c r="C76" s="77"/>
       <c r="D76" s="34" t="s">
         <v>784</v>
       </c>
-      <c r="E76" s="92" t="s">
+      <c r="E76" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="F76" s="92" t="s">
+      <c r="F76" s="78" t="s">
         <v>785</v>
       </c>
       <c r="G76" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="H76" s="92"/>
-      <c r="I76" s="92" t="s">
+      <c r="H76" s="78"/>
+      <c r="I76" s="78" t="s">
         <v>786</v>
       </c>
-      <c r="J76" s="100" t="s">
+      <c r="J76" s="85" t="s">
         <v>800</v>
       </c>
-      <c r="K76" s="94"/>
-      <c r="L76" s="91"/>
-    </row>
-    <row r="77" spans="1:12" s="95" customFormat="1" ht="62" x14ac:dyDescent="0.35">
-      <c r="A77" s="91"/>
-      <c r="B77" s="91"/>
-      <c r="C77" s="91"/>
-      <c r="D77" s="92" t="s">
+      <c r="K76" s="77"/>
+    </row>
+    <row r="77" spans="1:11" s="80" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A77" s="77"/>
+      <c r="B77" s="77"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="78" t="s">
         <v>787</v>
       </c>
-      <c r="E77" s="92" t="s">
+      <c r="E77" s="78" t="s">
         <v>17</v>
       </c>
       <c r="F77" s="34" t="s">
@@ -9401,249 +9345,241 @@
       <c r="G77" s="62" t="s">
         <v>799</v>
       </c>
-      <c r="H77" s="92"/>
+      <c r="H77" s="78"/>
       <c r="I77" s="62" t="s">
         <v>789</v>
       </c>
-      <c r="J77" s="92" t="s">
+      <c r="J77" s="78" t="s">
         <v>801</v>
       </c>
-      <c r="K77" s="94"/>
-      <c r="L77" s="91"/>
-    </row>
-    <row r="78" spans="1:12" s="95" customFormat="1" ht="62" x14ac:dyDescent="0.35">
-      <c r="A78" s="91"/>
-      <c r="B78" s="91"/>
-      <c r="C78" s="91"/>
+      <c r="K77" s="77"/>
+    </row>
+    <row r="78" spans="1:11" s="80" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+      <c r="A78" s="77"/>
+      <c r="B78" s="77"/>
+      <c r="C78" s="77"/>
       <c r="D78" s="34" t="s">
         <v>790</v>
       </c>
-      <c r="E78" s="92" t="s">
+      <c r="E78" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="F78" s="92" t="s">
+      <c r="F78" s="78" t="s">
         <v>791</v>
       </c>
-      <c r="G78" s="92" t="s">
+      <c r="G78" s="78" t="s">
         <v>792</v>
       </c>
-      <c r="H78" s="92"/>
-      <c r="I78" s="92" t="s">
+      <c r="H78" s="78"/>
+      <c r="I78" s="78" t="s">
         <v>793</v>
       </c>
-      <c r="J78" s="101" t="s">
+      <c r="J78" s="86" t="s">
         <v>802</v>
       </c>
-      <c r="K78" s="94"/>
-      <c r="L78" s="91"/>
-    </row>
-    <row r="79" spans="1:12" s="95" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="91"/>
-      <c r="B79" s="91"/>
-      <c r="C79" s="91"/>
-      <c r="D79" s="92" t="s">
+      <c r="K78" s="77"/>
+    </row>
+    <row r="79" spans="1:11" s="80" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="77"/>
+      <c r="B79" s="77"/>
+      <c r="C79" s="77"/>
+      <c r="D79" s="78" t="s">
         <v>794</v>
       </c>
-      <c r="E79" s="92" t="s">
+      <c r="E79" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="F79" s="92" t="s">
+      <c r="F79" s="78" t="s">
         <v>795</v>
       </c>
-      <c r="G79" s="92" t="s">
+      <c r="G79" s="78" t="s">
         <v>796</v>
       </c>
-      <c r="H79" s="92"/>
-      <c r="I79" s="92" t="s">
+      <c r="H79" s="78"/>
+      <c r="I79" s="78" t="s">
         <v>797</v>
       </c>
-      <c r="J79" s="101" t="s">
+      <c r="J79" s="86" t="s">
         <v>803</v>
       </c>
-      <c r="K79" s="94"/>
-      <c r="L79" s="91"/>
-    </row>
-    <row r="80" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="76" t="s">
+      <c r="K79" s="77"/>
+    </row>
+    <row r="80" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B80" s="103" t="s">
         <v>302</v>
       </c>
-      <c r="C80" s="76"/>
-      <c r="D80" s="76"/>
-      <c r="E80" s="76"/>
-      <c r="F80" s="76"/>
-      <c r="G80" s="76"/>
-      <c r="H80" s="76"/>
-      <c r="I80" s="76"/>
-      <c r="J80" s="76"/>
-    </row>
-    <row r="81" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C81" s="77" t="s">
+      <c r="C80" s="103"/>
+      <c r="D80" s="103"/>
+      <c r="E80" s="103"/>
+      <c r="F80" s="103"/>
+      <c r="G80" s="103"/>
+      <c r="H80" s="103"/>
+      <c r="I80" s="103"/>
+      <c r="J80" s="103"/>
+    </row>
+    <row r="81" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C81" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D81" s="77"/>
-      <c r="E81" s="77"/>
-      <c r="F81" s="77"/>
-      <c r="G81" s="77"/>
-      <c r="H81" s="77"/>
-      <c r="I81" s="77"/>
-      <c r="J81" s="77"/>
-    </row>
-    <row r="82" spans="2:12" s="95" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B82" s="91"/>
-      <c r="C82" s="91"/>
-      <c r="D82" s="92" t="s">
+      <c r="D81" s="104"/>
+      <c r="E81" s="104"/>
+      <c r="F81" s="104"/>
+      <c r="G81" s="104"/>
+      <c r="H81" s="104"/>
+      <c r="I81" s="104"/>
+      <c r="J81" s="104"/>
+    </row>
+    <row r="82" spans="2:11" s="80" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="77"/>
+      <c r="C82" s="77"/>
+      <c r="D82" s="78" t="s">
         <v>814</v>
       </c>
-      <c r="E82" s="92" t="s">
+      <c r="E82" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="F82" s="92" t="s">
+      <c r="F82" s="78" t="s">
         <v>822</v>
       </c>
-      <c r="G82" s="92" t="s">
+      <c r="G82" s="78" t="s">
         <v>830</v>
       </c>
-      <c r="H82" s="92"/>
-      <c r="I82" s="92" t="s">
+      <c r="H82" s="78"/>
+      <c r="I82" s="78" t="s">
         <v>815</v>
       </c>
-      <c r="J82" s="92" t="s">
+      <c r="J82" s="78" t="s">
         <v>823</v>
       </c>
-      <c r="K82" s="94"/>
-      <c r="L82" s="99"/>
-    </row>
-    <row r="83" spans="2:12" s="95" customFormat="1" ht="93" x14ac:dyDescent="0.35">
-      <c r="B83" s="91"/>
-      <c r="C83" s="91"/>
-      <c r="D83" s="92" t="s">
+      <c r="K82" s="84"/>
+    </row>
+    <row r="83" spans="2:11" s="80" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="B83" s="77"/>
+      <c r="C83" s="77"/>
+      <c r="D83" s="78" t="s">
         <v>816</v>
       </c>
-      <c r="E83" s="92" t="s">
+      <c r="E83" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="F83" s="92" t="s">
+      <c r="F83" s="78" t="s">
         <v>824</v>
       </c>
-      <c r="G83" s="92" t="s">
+      <c r="G83" s="78" t="s">
         <v>811</v>
       </c>
-      <c r="H83" s="92"/>
-      <c r="I83" s="92" t="s">
+      <c r="H83" s="78"/>
+      <c r="I83" s="78" t="s">
         <v>817</v>
       </c>
-      <c r="J83" s="92" t="s">
+      <c r="J83" s="78" t="s">
         <v>825</v>
       </c>
-      <c r="K83" s="94"/>
-      <c r="L83" s="99"/>
-    </row>
-    <row r="84" spans="2:12" s="95" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="91"/>
-      <c r="C84" s="91"/>
-      <c r="D84" s="92" t="s">
+      <c r="K83" s="84"/>
+    </row>
+    <row r="84" spans="2:11" s="80" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="77"/>
+      <c r="C84" s="77"/>
+      <c r="D84" s="78" t="s">
         <v>818</v>
       </c>
-      <c r="E84" s="92" t="s">
+      <c r="E84" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="F84" s="92" t="s">
+      <c r="F84" s="78" t="s">
         <v>826</v>
       </c>
-      <c r="G84" s="92" t="s">
+      <c r="G84" s="78" t="s">
         <v>812</v>
       </c>
-      <c r="H84" s="92"/>
-      <c r="I84" s="92" t="s">
+      <c r="H84" s="78"/>
+      <c r="I84" s="78" t="s">
         <v>819</v>
       </c>
-      <c r="J84" s="92" t="s">
+      <c r="J84" s="78" t="s">
         <v>827</v>
       </c>
-      <c r="K84" s="94"/>
-      <c r="L84" s="99"/>
-    </row>
-    <row r="85" spans="2:12" s="95" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="91"/>
-      <c r="C85" s="91"/>
-      <c r="D85" s="92" t="s">
+      <c r="K84" s="84"/>
+    </row>
+    <row r="85" spans="2:11" s="80" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="77"/>
+      <c r="C85" s="77"/>
+      <c r="D85" s="78" t="s">
         <v>820</v>
       </c>
-      <c r="E85" s="92" t="s">
+      <c r="E85" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="F85" s="92" t="s">
+      <c r="F85" s="78" t="s">
         <v>828</v>
       </c>
-      <c r="G85" s="92" t="s">
+      <c r="G85" s="78" t="s">
         <v>813</v>
       </c>
-      <c r="H85" s="92"/>
-      <c r="I85" s="92" t="s">
+      <c r="H85" s="78"/>
+      <c r="I85" s="78" t="s">
         <v>821</v>
       </c>
-      <c r="J85" s="92" t="s">
+      <c r="J85" s="78" t="s">
         <v>829</v>
       </c>
-      <c r="K85" s="94"/>
-      <c r="L85" s="99"/>
-    </row>
-    <row r="86" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="76" t="s">
+      <c r="K85" s="84"/>
+    </row>
+    <row r="86" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B86" s="103" t="s">
         <v>319</v>
       </c>
-      <c r="C86" s="76"/>
-      <c r="D86" s="76"/>
-      <c r="E86" s="76"/>
-      <c r="F86" s="76"/>
-      <c r="G86" s="76"/>
-      <c r="H86" s="76"/>
-      <c r="I86" s="76"/>
-      <c r="J86" s="76"/>
-    </row>
-    <row r="87" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C87" s="77" t="s">
+      <c r="C86" s="103"/>
+      <c r="D86" s="103"/>
+      <c r="E86" s="103"/>
+      <c r="F86" s="103"/>
+      <c r="G86" s="103"/>
+      <c r="H86" s="103"/>
+      <c r="I86" s="103"/>
+      <c r="J86" s="103"/>
+    </row>
+    <row r="87" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C87" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D87" s="77"/>
-      <c r="E87" s="77"/>
-      <c r="F87" s="77"/>
-      <c r="G87" s="77"/>
-      <c r="H87" s="77"/>
-      <c r="I87" s="77"/>
-      <c r="J87" s="77"/>
-    </row>
-    <row r="88" spans="2:12" ht="93" x14ac:dyDescent="0.35">
+      <c r="D87" s="104"/>
+      <c r="E87" s="104"/>
+      <c r="F87" s="104"/>
+      <c r="G87" s="104"/>
+      <c r="H87" s="104"/>
+      <c r="I87" s="104"/>
+      <c r="J87" s="104"/>
+    </row>
+    <row r="88" spans="2:11" ht="102" x14ac:dyDescent="0.2">
       <c r="B88" s="18"/>
       <c r="C88" s="18"/>
-      <c r="D88" s="102" t="s">
+      <c r="D88" s="87" t="s">
         <v>840</v>
       </c>
-      <c r="E88" s="102" t="s">
+      <c r="E88" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="F88" s="102" t="s">
+      <c r="F88" s="87" t="s">
         <v>841</v>
       </c>
       <c r="G88" s="32" t="s">
         <v>831</v>
       </c>
-      <c r="H88" s="102"/>
-      <c r="I88" s="102" t="s">
+      <c r="H88" s="87"/>
+      <c r="I88" s="87" t="s">
         <v>832</v>
       </c>
-      <c r="J88" s="103" t="s">
+      <c r="J88" s="88" t="s">
         <v>842</v>
       </c>
-      <c r="K88" s="94"/>
-    </row>
-    <row r="89" spans="2:12" ht="81" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="2:11" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
       <c r="D89" s="13" t="s">
         <v>843</v>
       </c>
-      <c r="E89" s="102" t="s">
+      <c r="E89" s="87" t="s">
         <v>17</v>
       </c>
       <c r="F89" s="32" t="s">
@@ -9652,87 +9588,84 @@
       <c r="G89" s="41" t="s">
         <v>833</v>
       </c>
-      <c r="H89" s="102"/>
+      <c r="H89" s="87"/>
       <c r="I89" s="41" t="s">
         <v>834</v>
       </c>
-      <c r="J89" s="104" t="s">
+      <c r="J89" s="89" t="s">
         <v>845</v>
       </c>
-      <c r="K89" s="94"/>
-    </row>
-    <row r="90" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="B90" s="18"/>
       <c r="C90" s="18"/>
       <c r="D90" s="32" t="s">
         <v>835</v>
       </c>
-      <c r="E90" s="102" t="s">
+      <c r="E90" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="F90" s="102" t="s">
+      <c r="F90" s="87" t="s">
         <v>836</v>
       </c>
-      <c r="G90" s="102" t="s">
+      <c r="G90" s="87" t="s">
         <v>849</v>
       </c>
-      <c r="H90" s="102"/>
+      <c r="H90" s="87"/>
       <c r="I90" s="41" t="s">
         <v>837</v>
       </c>
-      <c r="J90" s="105"/>
-      <c r="K90" s="94"/>
-    </row>
-    <row r="91" spans="2:12" ht="81" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J90" s="90"/>
+    </row>
+    <row r="91" spans="2:11" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B91" s="18"/>
       <c r="C91" s="18"/>
-      <c r="D91" s="102" t="s">
+      <c r="D91" s="87" t="s">
         <v>846</v>
       </c>
-      <c r="E91" s="102" t="s">
+      <c r="E91" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="F91" s="102" t="s">
+      <c r="F91" s="87" t="s">
         <v>847</v>
       </c>
-      <c r="G91" s="102" t="s">
+      <c r="G91" s="87" t="s">
         <v>838</v>
       </c>
-      <c r="H91" s="102"/>
-      <c r="I91" s="102" t="s">
+      <c r="H91" s="87"/>
+      <c r="I91" s="87" t="s">
         <v>839</v>
       </c>
-      <c r="J91" s="105" t="s">
+      <c r="J91" s="90" t="s">
         <v>848</v>
       </c>
-      <c r="K91" s="94"/>
-    </row>
-    <row r="92" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="76" t="s">
+    </row>
+    <row r="92" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="B92" s="103" t="s">
         <v>338</v>
       </c>
-      <c r="C92" s="76"/>
-      <c r="D92" s="76"/>
-      <c r="E92" s="76"/>
-      <c r="F92" s="76"/>
-      <c r="G92" s="76"/>
-      <c r="H92" s="76"/>
-      <c r="I92" s="76"/>
-      <c r="J92" s="76"/>
-    </row>
-    <row r="93" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C93" s="77" t="s">
+      <c r="C92" s="103"/>
+      <c r="D92" s="103"/>
+      <c r="E92" s="103"/>
+      <c r="F92" s="103"/>
+      <c r="G92" s="103"/>
+      <c r="H92" s="103"/>
+      <c r="I92" s="103"/>
+      <c r="J92" s="103"/>
+    </row>
+    <row r="93" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C93" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D93" s="77"/>
-      <c r="E93" s="77"/>
-      <c r="F93" s="77"/>
-      <c r="G93" s="77"/>
-      <c r="H93" s="77"/>
-      <c r="I93" s="77"/>
-      <c r="J93" s="77"/>
-    </row>
-    <row r="94" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="D93" s="104"/>
+      <c r="E93" s="104"/>
+      <c r="F93" s="104"/>
+      <c r="G93" s="104"/>
+      <c r="H93" s="104"/>
+      <c r="I93" s="104"/>
+      <c r="J93" s="104"/>
+    </row>
+    <row r="94" spans="2:11" ht="68" x14ac:dyDescent="0.2">
       <c r="B94" s="18"/>
       <c r="C94" s="18"/>
       <c r="D94" s="30" t="s">
@@ -9751,12 +9684,11 @@
       <c r="I94" s="27" t="s">
         <v>853</v>
       </c>
-      <c r="J94" s="93" t="s">
+      <c r="J94" s="79" t="s">
         <v>854</v>
       </c>
-      <c r="K94" s="94"/>
-    </row>
-    <row r="95" spans="2:12" ht="46.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="2:11" ht="51" x14ac:dyDescent="0.2">
       <c r="B95" s="18"/>
       <c r="C95" s="18"/>
       <c r="D95" s="27" t="s">
@@ -9775,12 +9707,11 @@
       <c r="I95" s="31" t="s">
         <v>857</v>
       </c>
-      <c r="J95" s="100" t="s">
+      <c r="J95" s="85" t="s">
         <v>858</v>
       </c>
-      <c r="K95" s="94"/>
-    </row>
-    <row r="96" spans="2:12" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="2:11" ht="51" x14ac:dyDescent="0.2">
       <c r="B96" s="18"/>
       <c r="C96" s="18"/>
       <c r="D96" s="30" t="s">
@@ -9799,12 +9730,11 @@
       <c r="I96" s="27" t="s">
         <v>862</v>
       </c>
-      <c r="J96" s="101" t="s">
+      <c r="J96" s="86" t="s">
         <v>863</v>
       </c>
-      <c r="K96" s="94"/>
-    </row>
-    <row r="97" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="B97" s="18"/>
       <c r="C97" s="18"/>
       <c r="D97" s="27" t="s">
@@ -9816,141 +9746,158 @@
       <c r="F97" s="27" t="s">
         <v>865</v>
       </c>
-      <c r="G97" s="102" t="s">
+      <c r="G97" s="87" t="s">
         <v>869</v>
       </c>
       <c r="H97" s="27"/>
       <c r="I97" s="27" t="s">
         <v>866</v>
       </c>
-      <c r="J97" s="101" t="s">
+      <c r="J97" s="86" t="s">
         <v>867</v>
       </c>
-      <c r="K97" s="94"/>
-    </row>
-    <row r="98" spans="2:11" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="76" t="s">
+    </row>
+    <row r="98" spans="2:10" ht="24" x14ac:dyDescent="0.3">
+      <c r="B98" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="C98" s="76"/>
-      <c r="D98" s="76"/>
-      <c r="E98" s="76"/>
-      <c r="F98" s="76"/>
-      <c r="G98" s="76"/>
-      <c r="H98" s="76"/>
-      <c r="I98" s="76"/>
-      <c r="J98" s="76"/>
-    </row>
-    <row r="99" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="77" t="s">
+      <c r="C98" s="103"/>
+      <c r="D98" s="103"/>
+      <c r="E98" s="103"/>
+      <c r="F98" s="103"/>
+      <c r="G98" s="103"/>
+      <c r="H98" s="103"/>
+      <c r="I98" s="103"/>
+      <c r="J98" s="103"/>
+    </row>
+    <row r="99" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C99" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D99" s="77"/>
-      <c r="E99" s="77"/>
-      <c r="F99" s="77"/>
-      <c r="G99" s="77"/>
-      <c r="H99" s="77"/>
-      <c r="I99" s="77"/>
-      <c r="J99" s="77"/>
-    </row>
-    <row r="100" spans="2:11" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="D99" s="104"/>
+      <c r="E99" s="104"/>
+      <c r="F99" s="104"/>
+      <c r="G99" s="104"/>
+      <c r="H99" s="104"/>
+      <c r="I99" s="104"/>
+      <c r="J99" s="104"/>
+    </row>
+    <row r="100" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
-      <c r="D100" s="92" t="s">
+      <c r="D100" s="78" t="s">
         <v>870</v>
       </c>
-      <c r="E100" s="92" t="s">
+      <c r="E100" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="F100" s="92" t="s">
+      <c r="F100" s="78" t="s">
         <v>871</v>
       </c>
       <c r="G100" s="34" t="s">
         <v>887</v>
       </c>
-      <c r="H100" s="92"/>
+      <c r="H100" s="78"/>
       <c r="I100" s="34" t="s">
         <v>872</v>
       </c>
-      <c r="J100" s="93" t="s">
+      <c r="J100" s="79" t="s">
         <v>885</v>
       </c>
-      <c r="K100" s="94"/>
-    </row>
-    <row r="101" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="B101" s="18"/>
       <c r="C101" s="18"/>
-      <c r="D101" s="92" t="s">
+      <c r="D101" s="78" t="s">
         <v>873</v>
       </c>
-      <c r="E101" s="92" t="s">
+      <c r="E101" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="F101" s="92" t="s">
+      <c r="F101" s="78" t="s">
         <v>874</v>
       </c>
       <c r="G101" s="34" t="s">
         <v>875</v>
       </c>
-      <c r="H101" s="92"/>
+      <c r="H101" s="78"/>
       <c r="I101" s="34" t="s">
         <v>876</v>
       </c>
-      <c r="J101" s="100" t="s">
+      <c r="J101" s="85" t="s">
         <v>877</v>
       </c>
-      <c r="K101" s="94"/>
-    </row>
-    <row r="102" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="B102" s="18"/>
       <c r="C102" s="18"/>
-      <c r="D102" s="92" t="s">
+      <c r="D102" s="78" t="s">
         <v>878</v>
       </c>
-      <c r="E102" s="92" t="s">
+      <c r="E102" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="F102" s="92" t="s">
+      <c r="F102" s="78" t="s">
         <v>879</v>
       </c>
       <c r="G102" s="34" t="s">
         <v>888</v>
       </c>
-      <c r="H102" s="92"/>
+      <c r="H102" s="78"/>
       <c r="I102" s="34" t="s">
         <v>880</v>
       </c>
-      <c r="J102" s="101" t="s">
+      <c r="J102" s="86" t="s">
         <v>886</v>
       </c>
-      <c r="K102" s="94"/>
-    </row>
-    <row r="103" spans="2:11" ht="62" x14ac:dyDescent="0.35">
+    </row>
+    <row r="103" spans="2:10" ht="68" x14ac:dyDescent="0.2">
       <c r="B103" s="18"/>
       <c r="C103" s="18"/>
-      <c r="D103" s="92" t="s">
+      <c r="D103" s="78" t="s">
         <v>881</v>
       </c>
-      <c r="E103" s="92" t="s">
+      <c r="E103" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="F103" s="92" t="s">
+      <c r="F103" s="78" t="s">
         <v>882</v>
       </c>
       <c r="G103" s="34" t="s">
         <v>889</v>
       </c>
-      <c r="H103" s="92"/>
+      <c r="H103" s="78"/>
       <c r="I103" s="34" t="s">
         <v>883</v>
       </c>
-      <c r="J103" s="101" t="s">
+      <c r="J103" s="86" t="s">
         <v>884</v>
       </c>
-      <c r="K103" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C87:J87"/>
+    <mergeCell ref="B92:J92"/>
+    <mergeCell ref="C93:J93"/>
+    <mergeCell ref="B98:J98"/>
+    <mergeCell ref="C99:J99"/>
+    <mergeCell ref="B74:J74"/>
+    <mergeCell ref="C75:J75"/>
+    <mergeCell ref="B80:J80"/>
+    <mergeCell ref="C81:J81"/>
+    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="C69:J69"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="B50:J50"/>
+    <mergeCell ref="C51:J51"/>
+    <mergeCell ref="B56:J56"/>
+    <mergeCell ref="C57:J57"/>
+    <mergeCell ref="B62:J62"/>
+    <mergeCell ref="C63:J63"/>
+    <mergeCell ref="C39:J39"/>
     <mergeCell ref="B26:J26"/>
     <mergeCell ref="C45:J45"/>
     <mergeCell ref="B2:J2"/>
@@ -9963,28 +9910,6 @@
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="C21:J21"/>
-    <mergeCell ref="C69:J69"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="B68:J68"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="C33:J33"/>
-    <mergeCell ref="B50:J50"/>
-    <mergeCell ref="C51:J51"/>
-    <mergeCell ref="B56:J56"/>
-    <mergeCell ref="C57:J57"/>
-    <mergeCell ref="B62:J62"/>
-    <mergeCell ref="C63:J63"/>
-    <mergeCell ref="C39:J39"/>
-    <mergeCell ref="B74:J74"/>
-    <mergeCell ref="C75:J75"/>
-    <mergeCell ref="B80:J80"/>
-    <mergeCell ref="C81:J81"/>
-    <mergeCell ref="B86:J86"/>
-    <mergeCell ref="C87:J87"/>
-    <mergeCell ref="B92:J92"/>
-    <mergeCell ref="C93:J93"/>
-    <mergeCell ref="B98:J98"/>
-    <mergeCell ref="C99:J99"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -10006,14 +9931,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{359B53C1-931A-41F0-A75B-DA74F397778B}">
   <dimension ref="B2:R19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
       <c r="R2" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>376</v>
       </c>
@@ -10021,7 +9946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>378</v>
       </c>
@@ -10029,7 +9954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>379</v>
       </c>
@@ -10037,7 +9962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>380</v>
       </c>
@@ -10045,7 +9970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>381</v>
       </c>
@@ -10053,7 +9978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>382</v>
       </c>
@@ -10061,17 +9986,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="R9" s="7">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
       <c r="R10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="P11" t="s">
         <v>383</v>
       </c>
@@ -10079,7 +10004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="P12" s="7">
         <v>6</v>
       </c>
@@ -10087,7 +10012,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="P13" s="7">
         <v>8</v>
       </c>
@@ -10095,7 +10020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
       <c r="P14" s="7">
         <v>12</v>
       </c>
@@ -10103,7 +10028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
       <c r="P15">
         <v>14</v>
       </c>
@@ -10111,7 +10036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
       <c r="P16">
         <v>10</v>
       </c>
@@ -10119,7 +10044,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="16:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="16:18" x14ac:dyDescent="0.2">
       <c r="P17">
         <v>5</v>
       </c>
@@ -10127,7 +10052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="16:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="16:18" x14ac:dyDescent="0.2">
       <c r="P18">
         <v>17</v>
       </c>
@@ -10135,7 +10060,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="16:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="16:18" x14ac:dyDescent="0.2">
       <c r="P19">
         <v>13</v>
       </c>
@@ -10146,15 +10071,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A2E062043278E0498B3F175803BDD307" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="f9d1e7cf378a7f0e14b1e4c8c2ac706a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e5b2aacb-65fb-44a3-9fbc-58e175cd9687" xmlns:ns3="c58d22d8-e609-4e82-843f-37202020edd3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2fa76803201a4ee85711379ea389746f" ns2:_="" ns3:_="">
     <xsd:import namespace="e5b2aacb-65fb-44a3-9fbc-58e175cd9687"/>
@@ -10389,6 +10305,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10401,14 +10326,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3481A49-1E9B-4B14-B14D-D0C150E9895E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1789FBBE-1BA9-4BFA-8489-91450F62273C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10427,6 +10344,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3481A49-1E9B-4B14-B14D-D0C150E9895E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C709CC8-42D8-440F-B2C7-C80CD306A5CD}">
   <ds:schemaRefs>
